--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,6 +481,8 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,65 +533,75 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Actual FY23-24</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Actual FY24-25</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>FY24-25</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -638,25 +650,25 @@
         <v>132</v>
       </c>
       <c r="J2" s="5" t="n">
+        <v>0.05408598823176547</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.1498933489306341</v>
+      </c>
+      <c r="L2" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>0.8446</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="O2" s="5" t="n">
         <v>0.8698</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="P2" s="5" t="n">
         <v>0.8245</v>
-      </c>
-      <c r="O2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -665,15 +677,21 @@
         <v>0</v>
       </c>
       <c r="S2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U2" s="6" t="n">
+      <c r="W2" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V2" s="6" t="n">
+      <c r="X2" s="6" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -720,42 +738,48 @@
         <v>66</v>
       </c>
       <c r="J3" s="5" t="n">
+        <v>0.05478264603755456</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.1357018019333979</v>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>0.9182</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="O3" s="5" t="n">
         <v>0.9284</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="P3" s="5" t="n">
         <v>0.9235</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="Q3" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="R3" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="S3" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="T3" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="U3" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="V3" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="W3" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -802,25 +826,25 @@
         <v>132</v>
       </c>
       <c r="J4" s="5" t="n">
+        <v>0.1440247773689721</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.1299222960127742</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>0.8719</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="O4" s="5" t="n">
         <v>0.9187</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="P4" s="5" t="n">
         <v>0.869</v>
-      </c>
-      <c r="O4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -829,15 +853,21 @@
         <v>0</v>
       </c>
       <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="V4" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="W4" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -884,42 +914,48 @@
         <v>22</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>0.1211386533906305</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.156935340089925</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>0.399270575823056</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.017550018083952</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.7784</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>0.8642</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="P5" s="5" t="n">
         <v>0.8405</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="S5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="T5" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="U5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.06999999999999999</v>
       </c>
     </row>
@@ -961,23 +997,25 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="n">
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="n">
         <v>0.9751</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="O6" s="5" t="n">
         <v>0.9954</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.9961</v>
       </c>
-      <c r="O6" s="6" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="6" t="inlineStr"/>
       <c r="T6" s="6" t="inlineStr"/>
       <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
+      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1022,28 +1060,34 @@
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
+        <v>0.03269498787171465</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.02926126425553777</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>0.8367</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="O7" s="5" t="n">
         <v>0.873</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="P7" s="5" t="n">
         <v>0.825</v>
       </c>
-      <c r="O7" s="6" t="inlineStr"/>
-      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="6" t="inlineStr"/>
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
+      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1088,42 +1132,48 @@
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
+        <v>0.09614342553807431</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.08192117087777062</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>0.529503172508041</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>7.253613938629221e-05</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="N8" s="5" t="n">
         <v>0.8979</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="O8" s="5" t="n">
         <v>0.9355</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="P8" s="5" t="n">
         <v>0.8778</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="R8" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="S8" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="T8" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="U8" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="V8" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="W8" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="V8" s="6" t="n">
+      <c r="X8" s="6" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -1164,24 +1214,28 @@
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="n">
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="n">
         <v>0.9167</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="O9" s="5" t="n">
         <v>0.9278</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>0.8853</v>
       </c>
-      <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1226,28 +1280,34 @@
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>0.06953767632819552</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.0882066342370772</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.8439</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="O10" s="5" t="n">
         <v>0.8854</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="P10" s="5" t="n">
         <v>0.8395</v>
       </c>
-      <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="6" t="inlineStr"/>
       <c r="T10" s="6" t="inlineStr"/>
       <c r="U10" s="6" t="inlineStr"/>
       <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1292,28 +1352,34 @@
         <v>132</v>
       </c>
       <c r="J11" s="5" t="n">
+        <v>0.07039079639714096</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.08061793088892344</v>
+      </c>
+      <c r="L11" s="5" t="n">
         <v>0.7032826997896851</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>0.264676213474225</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>0.8651</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="O11" s="5" t="n">
         <v>0.8898</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="P11" s="5" t="n">
         <v>0.8387</v>
       </c>
-      <c r="O11" s="6" t="inlineStr"/>
-      <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="6" t="inlineStr"/>
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
       <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
+      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1354,20 +1420,22 @@
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="n">
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="n">
         <v>0.9255</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="P12" s="5" t="n">
         <v>0.884</v>
       </c>
-      <c r="O12" s="6" t="inlineStr"/>
-      <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="6" t="inlineStr"/>
       <c r="R12" s="6" t="inlineStr"/>
       <c r="S12" s="6" t="inlineStr"/>
       <c r="T12" s="6" t="inlineStr"/>
       <c r="U12" s="6" t="inlineStr"/>
       <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="6" t="inlineStr"/>
+      <c r="X12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1412,42 +1480,48 @@
         <v>66</v>
       </c>
       <c r="J13" s="5" t="n">
+        <v>0.138756180474872</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.3633793594193425</v>
+      </c>
+      <c r="L13" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.8969</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="O13" s="5" t="n">
         <v>0.8888</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="P13" s="5" t="n">
         <v>0.8827</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="Q13" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="R13" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="S13" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="T13" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="U13" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="V13" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="W13" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="X13" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -1493,29 +1567,31 @@
       <c r="I14" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>0.8424</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="O14" s="5" t="n">
         <v>0.8921</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="P14" s="5" t="n">
         <v>0.8493000000000001</v>
       </c>
-      <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="6" t="inlineStr"/>
       <c r="T14" s="6" t="inlineStr"/>
       <c r="U14" s="6" t="inlineStr"/>
       <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
+      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1560,28 +1636,34 @@
         <v>330</v>
       </c>
       <c r="J15" s="5" t="n">
+        <v>0.03485234997163289</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.1455688224294164</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>0.165388664850326</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.000681438300925263</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.9498</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="P15" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="O15" s="6" t="inlineStr"/>
-      <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr"/>
       <c r="R15" s="6" t="inlineStr"/>
       <c r="S15" s="6" t="inlineStr"/>
       <c r="T15" s="6" t="inlineStr"/>
       <c r="U15" s="6" t="inlineStr"/>
       <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="6" t="inlineStr"/>
+      <c r="X15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1626,42 +1708,48 @@
         <v>132</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>0.1353701649733416</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.1888177292264882</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>0.903607825126104</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>0.900375357730696</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="N16" s="5" t="n">
         <v>0.8394</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="O16" s="5" t="n">
         <v>0.8437</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="P16" s="5" t="n">
         <v>0.8473000000000001</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="Q16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="R16" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="S16" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="T16" s="6" t="n">
         <v>0.006666666666666667</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="U16" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="V16" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="W16" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="X16" s="6" t="n">
         <v>0.07666666666666667</v>
       </c>
     </row>
@@ -1708,28 +1796,34 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
+        <v>0.1441759394227755</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.3082526071352186</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.8482</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="O17" s="5" t="n">
         <v>0.8888</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="P17" s="5" t="n">
         <v>0.848</v>
       </c>
-      <c r="O17" s="6" t="inlineStr"/>
-      <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
       <c r="R17" s="6" t="inlineStr"/>
       <c r="S17" s="6" t="inlineStr"/>
       <c r="T17" s="6" t="inlineStr"/>
       <c r="U17" s="6" t="inlineStr"/>
       <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="6" t="inlineStr"/>
+      <c r="X17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1774,28 +1868,34 @@
         <v>66</v>
       </c>
       <c r="J18" s="5" t="n">
+        <v>0.07290536050268626</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.1189868785607631</v>
+      </c>
+      <c r="L18" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>0.8943</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="O18" s="5" t="n">
         <v>0.8923</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="P18" s="5" t="n">
         <v>0.8823</v>
       </c>
-      <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
       <c r="S18" s="6" t="inlineStr"/>
       <c r="T18" s="6" t="inlineStr"/>
       <c r="U18" s="6" t="inlineStr"/>
       <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
+      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1840,25 +1940,25 @@
         <v>132</v>
       </c>
       <c r="J19" s="5" t="n">
+        <v>0.1624878107170906</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.2969960740318008</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.8752</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="O19" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="P19" s="5" t="n">
         <v>0.8725000000000001</v>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1867,15 +1967,21 @@
         <v>0</v>
       </c>
       <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="V19" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="W19" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="X19" s="6" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -1922,42 +2028,48 @@
         <v>220</v>
       </c>
       <c r="J20" s="5" t="n">
+        <v>0.1329559142410704</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.2548659571637795</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.7774</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="O20" s="5" t="n">
         <v>0.8529</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="P20" s="5" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="Q20" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="R20" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="S20" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="T20" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="U20" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="V20" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="W20" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="X20" s="6" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -2004,42 +2116,48 @@
         <v>22</v>
       </c>
       <c r="J21" s="5" t="n">
+        <v>0.1373179274132644</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.2539757919262627</v>
+      </c>
+      <c r="L21" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="N21" s="5" t="n">
         <v>0.7793</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="O21" s="5" t="n">
         <v>0.8528</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="P21" s="5" t="n">
         <v>0.8143</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="Q21" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="R21" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="S21" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="T21" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="U21" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="V21" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="W21" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="X21" s="6" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -2086,42 +2204,48 @@
         <v>132</v>
       </c>
       <c r="J22" s="5" t="n">
+        <v>0.5229812164970579</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.6709166872938147</v>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="M22" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="N22" s="5" t="n">
         <v>0.9540999999999999</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="O22" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="P22" s="5" t="n">
         <v>0.9397</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="Q22" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="R22" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="S22" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="T22" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="U22" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="V22" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="W22" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="X22" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -2168,42 +2292,48 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
+        <v>0.007190464584342027</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.07108174352041219</v>
+      </c>
+      <c r="L23" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="M23" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="N23" s="5" t="n">
         <v>0.8668</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="O23" s="5" t="n">
         <v>0.8557</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="P23" s="5" t="n">
         <v>0.8702</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="Q23" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="R23" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="S23" s="6" t="n">
         <v>0.24</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="T23" s="6" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="U23" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="V23" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="W23" s="6" t="n">
         <v>0.34</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="X23" s="6" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -2250,42 +2380,48 @@
         <v>66</v>
       </c>
       <c r="J24" s="5" t="n">
+        <v>0.5764125048753213</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.6755707391955864</v>
+      </c>
+      <c r="L24" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="M24" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="N24" s="5" t="n">
         <v>0.9616</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="O24" s="5" t="n">
         <v>0.9573</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="P24" s="5" t="n">
         <v>0.9517</v>
       </c>
-      <c r="O24" s="6" t="n">
+      <c r="Q24" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="R24" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="S24" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="T24" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="U24" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="V24" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="W24" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="X24" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -2332,42 +2468,48 @@
         <v>66</v>
       </c>
       <c r="J25" s="5" t="n">
+        <v>0.01188361985022102</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.001815619300523097</v>
+      </c>
+      <c r="L25" s="5" t="n">
         <v>0.188257195450457</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="M25" s="5" t="n">
         <v>0.0686562187806459</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="N25" s="5" t="n">
         <v>0.8086</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="O25" s="5" t="n">
         <v>0.8387</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="P25" s="5" t="n">
         <v>0.8541</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="R25" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="S25" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="T25" s="6" t="n">
         <v>0.006666666666666667</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="U25" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="V25" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="W25" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="X25" s="6" t="n">
         <v>0.07666666666666667</v>
       </c>
     </row>
@@ -2409,23 +2551,25 @@
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="n">
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="n">
         <v>0.9523</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="O26" s="5" t="n">
         <v>0.9821</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="P26" s="5" t="n">
         <v>0.9799</v>
       </c>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
       <c r="T26" s="6" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2469,29 +2613,31 @@
       <c r="I27" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="M27" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="N27" s="5" t="n">
         <v>0.9284</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="O27" s="5" t="n">
         <v>0.923</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="P27" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="O27" s="6" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2536,42 +2682,48 @@
         <v>132</v>
       </c>
       <c r="J28" s="5" t="n">
+        <v>0.03231345345515402</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.07990508599190627</v>
+      </c>
+      <c r="L28" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="M28" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="N28" s="5" t="n">
         <v>0.9284</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="O28" s="5" t="n">
         <v>0.923</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="P28" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="Q28" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="R28" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="S28" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="T28" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="U28" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="V28" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="W28" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="X28" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -2618,42 +2770,48 @@
         <v>330</v>
       </c>
       <c r="J29" s="5" t="n">
+        <v>0.09252848872869046</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.139740603518281</v>
+      </c>
+      <c r="L29" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="M29" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="N29" s="5" t="n">
         <v>0.8901</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="O29" s="5" t="n">
         <v>0.8803</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="P29" s="5" t="n">
         <v>0.8943</v>
       </c>
-      <c r="O29" s="6" t="n">
+      <c r="Q29" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="R29" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="S29" s="6" t="n">
         <v>0.24</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="T29" s="6" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="U29" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="V29" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="W29" s="6" t="n">
         <v>0.34</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="X29" s="6" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -2700,42 +2858,48 @@
         <v>330</v>
       </c>
       <c r="J30" s="5" t="n">
+        <v>0.09865070018729849</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.1267494122393782</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="M30" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>0.8901</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="O30" s="5" t="n">
         <v>0.8803</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="P30" s="5" t="n">
         <v>0.8943</v>
       </c>
-      <c r="O30" s="6" t="n">
+      <c r="Q30" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="R30" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="S30" s="6" t="n">
         <v>0.24</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="T30" s="6" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="U30" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="V30" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="W30" s="6" t="n">
         <v>0.34</v>
       </c>
-      <c r="V30" s="6" t="n">
+      <c r="X30" s="6" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -2782,42 +2946,48 @@
         <v>132</v>
       </c>
       <c r="J31" s="5" t="n">
+        <v>0.02789950205429714</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.03926636218841828</v>
+      </c>
+      <c r="L31" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="M31" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="N31" s="5" t="n">
         <v>0.9835</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="O31" s="5" t="n">
         <v>0.9792999999999999</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="P31" s="5" t="n">
         <v>0.9698</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="Q31" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="R31" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="S31" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="T31" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="U31" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="V31" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="W31" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V31" s="6" t="n">
+      <c r="X31" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -2864,28 +3034,34 @@
         <v>66</v>
       </c>
       <c r="J32" s="5" t="n">
+        <v>0.1275049435515178</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0.3039969269602842</v>
+      </c>
+      <c r="L32" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="M32" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="N32" s="5" t="n">
         <v>0.8969</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="O32" s="5" t="n">
         <v>0.8888</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="P32" s="5" t="n">
         <v>0.8827</v>
       </c>
-      <c r="O32" s="6" t="inlineStr"/>
-      <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2926,20 +3102,22 @@
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="n">
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="n">
         <v>1.019</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="P33" s="5" t="n">
         <v>0.8863</v>
       </c>
-      <c r="O33" s="6" t="inlineStr"/>
-      <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2979,23 +3157,25 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="n">
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="n">
         <v>0.9515</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="O34" s="5" t="n">
         <v>0.9814000000000001</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="P34" s="5" t="n">
         <v>0.9656</v>
       </c>
-      <c r="O34" s="6" t="inlineStr"/>
-      <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="inlineStr"/>
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3040,42 +3220,48 @@
         <v>220</v>
       </c>
       <c r="J35" s="5" t="n">
+        <v>0.1153540312661219</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.1173458509370597</v>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="M35" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="N35" s="5" t="n">
         <v>0.7774</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>0.8529</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>0.8098</v>
       </c>
-      <c r="O35" s="6" t="n">
+      <c r="Q35" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="R35" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q35" s="6" t="n">
+      <c r="S35" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="T35" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="S35" s="6" t="n">
+      <c r="U35" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="V35" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="U35" s="6" t="n">
+      <c r="W35" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="V35" s="6" t="n">
+      <c r="X35" s="6" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -3122,25 +3308,25 @@
         <v>132</v>
       </c>
       <c r="J36" s="5" t="n">
+        <v>0.1912183081095272</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.2595859755929798</v>
+      </c>
+      <c r="L36" s="5" t="n">
         <v>0.1571570475144</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="M36" s="5" t="n">
         <v>0.0362161714591237</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="N36" s="5" t="n">
         <v>0.8752</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="O36" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="P36" s="5" t="n">
         <v>0.8725000000000001</v>
-      </c>
-      <c r="O36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3149,15 +3335,21 @@
         <v>0</v>
       </c>
       <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T36" s="6" t="n">
+      <c r="V36" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U36" s="6" t="n">
+      <c r="W36" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V36" s="6" t="n">
+      <c r="X36" s="6" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -3203,29 +3395,31 @@
       <c r="I37" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="n">
         <v>0.167592623869037</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="M37" s="5" t="n">
         <v>0.000643212863569608</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="N37" s="5" t="n">
         <v>0.9284</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="O37" s="5" t="n">
         <v>0.923</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="P37" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="O37" s="6" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3269,43 +3463,47 @@
       <c r="I38" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="n">
+        <v>0.1421915117897189</v>
+      </c>
+      <c r="L38" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="M38" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="N38" s="5" t="n">
         <v>0.9422</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="O38" s="5" t="n">
         <v>0.9429</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="P38" s="5" t="n">
         <v>0.9421</v>
       </c>
-      <c r="O38" s="6" t="n">
+      <c r="Q38" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="R38" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q38" s="6" t="n">
+      <c r="S38" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="T38" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S38" s="6" t="n">
+      <c r="U38" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T38" s="6" t="n">
+      <c r="V38" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U38" s="6" t="n">
+      <c r="W38" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V38" s="6" t="n">
+      <c r="X38" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -3351,43 +3549,47 @@
       <c r="I39" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="n">
+        <v>0.1466186570287763</v>
+      </c>
+      <c r="L39" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="M39" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="N39" s="5" t="n">
         <v>0.9422</v>
       </c>
-      <c r="M39" s="5" t="n">
+      <c r="O39" s="5" t="n">
         <v>0.9429</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="P39" s="5" t="n">
         <v>0.9421</v>
       </c>
-      <c r="O39" s="6" t="n">
+      <c r="Q39" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="R39" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q39" s="6" t="n">
+      <c r="S39" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="T39" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S39" s="6" t="n">
+      <c r="U39" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="V39" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U39" s="6" t="n">
+      <c r="W39" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V39" s="6" t="n">
+      <c r="X39" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -3434,42 +3636,48 @@
         <v>132</v>
       </c>
       <c r="J40" s="5" t="n">
+        <v>0.1345570232002854</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.1216265245384226</v>
+      </c>
+      <c r="L40" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="M40" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="L40" s="5" t="n">
+      <c r="N40" s="5" t="n">
         <v>0.9096</v>
       </c>
-      <c r="M40" s="5" t="n">
+      <c r="O40" s="5" t="n">
         <v>0.9073</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="P40" s="5" t="n">
         <v>0.9054</v>
       </c>
-      <c r="O40" s="6" t="n">
+      <c r="Q40" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="R40" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q40" s="6" t="n">
+      <c r="S40" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="T40" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S40" s="6" t="n">
+      <c r="U40" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="V40" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U40" s="6" t="n">
+      <c r="W40" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V40" s="6" t="n">
+      <c r="X40" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -3516,25 +3724,25 @@
         <v>66</v>
       </c>
       <c r="J41" s="5" t="n">
+        <v>0.1713544037663096</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.2654827427546417</v>
+      </c>
+      <c r="L41" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="M41" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="N41" s="5" t="n">
         <v>0.872</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="O41" s="5" t="n">
         <v>0.9183</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="P41" s="5" t="n">
         <v>0.8686</v>
-      </c>
-      <c r="O41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3543,15 +3751,21 @@
         <v>0</v>
       </c>
       <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="V41" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U41" s="6" t="n">
+      <c r="W41" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="V41" s="6" t="n">
+      <c r="X41" s="6" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -3597,29 +3811,33 @@
       <c r="I42" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="n">
+        <v>0.1015077616127097</v>
+      </c>
+      <c r="L42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K42" s="5" t="n">
+      <c r="M42" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L42" s="5" t="n">
+      <c r="N42" s="5" t="n">
         <v>0.8853</v>
       </c>
-      <c r="M42" s="5" t="n">
+      <c r="O42" s="5" t="n">
         <v>0.9298</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="P42" s="5" t="n">
         <v>0.8796</v>
       </c>
-      <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3663,29 +3881,33 @@
       <c r="I43" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="n">
+        <v>0.08481628251174367</v>
+      </c>
+      <c r="L43" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K43" s="5" t="n">
+      <c r="M43" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L43" s="5" t="n">
+      <c r="N43" s="5" t="n">
         <v>0.8853</v>
       </c>
-      <c r="M43" s="5" t="n">
+      <c r="O43" s="5" t="n">
         <v>0.9298</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="P43" s="5" t="n">
         <v>0.8783</v>
       </c>
-      <c r="O43" s="6" t="inlineStr"/>
-      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3730,42 +3952,48 @@
         <v>330</v>
       </c>
       <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.06566494744533402</v>
+      </c>
+      <c r="L44" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="M44" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="L44" s="5" t="n">
+      <c r="N44" s="5" t="n">
         <v>0.9389</v>
       </c>
-      <c r="M44" s="5" t="n">
+      <c r="O44" s="5" t="n">
         <v>0.9339</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="P44" s="5" t="n">
         <v>0.9364</v>
       </c>
-      <c r="O44" s="6" t="n">
+      <c r="Q44" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="R44" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="S44" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="T44" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S44" s="6" t="n">
+      <c r="U44" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="V44" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U44" s="6" t="n">
+      <c r="W44" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V44" s="6" t="n">
+      <c r="X44" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -3812,42 +4040,48 @@
         <v>132</v>
       </c>
       <c r="J45" s="5" t="n">
+        <v>0.03240949212773014</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.03166342025536539</v>
+      </c>
+      <c r="L45" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="M45" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="N45" s="5" t="n">
         <v>0.9284</v>
       </c>
-      <c r="M45" s="5" t="n">
+      <c r="O45" s="5" t="n">
         <v>0.923</v>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="P45" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="O45" s="6" t="n">
+      <c r="Q45" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="R45" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="S45" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="T45" s="6" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="S45" s="6" t="n">
+      <c r="U45" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="V45" s="6" t="n">
         <v>0.19</v>
       </c>
-      <c r="U45" s="6" t="n">
+      <c r="W45" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="V45" s="6" t="n">
+      <c r="X45" s="6" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -3894,28 +4128,34 @@
         <v>132</v>
       </c>
       <c r="J46" s="5" t="n">
+        <v>0.1526525054987787</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.1992808636220385</v>
+      </c>
+      <c r="L46" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="M46" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="L46" s="5" t="n">
+      <c r="N46" s="5" t="n">
         <v>0.8752</v>
       </c>
-      <c r="M46" s="5" t="n">
+      <c r="O46" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="P46" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="6" t="inlineStr"/>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3960,42 +4200,48 @@
         <v>132</v>
       </c>
       <c r="J47" s="5" t="n">
+        <v>0.06560284749189083</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0.06534439203754416</v>
+      </c>
+      <c r="L47" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="M47" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="L47" s="5" t="n">
+      <c r="N47" s="5" t="n">
         <v>0.8453000000000001</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="O47" s="5" t="n">
         <v>0.8149</v>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="P47" s="5" t="n">
         <v>0.8286</v>
       </c>
-      <c r="O47" s="6" t="n">
+      <c r="Q47" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P47" s="6" t="n">
+      <c r="R47" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="S47" s="6" t="n">
         <v>0.24</v>
       </c>
-      <c r="R47" s="6" t="n">
+      <c r="T47" s="6" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="S47" s="6" t="n">
+      <c r="U47" s="6" t="n">
         <v>0.16</v>
       </c>
-      <c r="T47" s="6" t="n">
+      <c r="V47" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="U47" s="6" t="n">
+      <c r="W47" s="6" t="n">
         <v>0.34</v>
       </c>
-      <c r="V47" s="6" t="n">
+      <c r="X47" s="6" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -4041,29 +4287,33 @@
       <c r="I48" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="n">
+        <v>0.2050867232572048</v>
+      </c>
+      <c r="L48" s="5" t="n">
         <v>0.158699742317549</v>
       </c>
-      <c r="K48" s="5" t="n">
+      <c r="M48" s="5" t="n">
         <v>0.000581408571101005</v>
       </c>
-      <c r="L48" s="5" t="n">
+      <c r="N48" s="5" t="n">
         <v>0.953</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="O48" s="5" t="n">
         <v>0.957</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="P48" s="5" t="n">
         <v>0.9548</v>
       </c>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4108,28 +4358,34 @@
         <v>132</v>
       </c>
       <c r="J49" s="5" t="n">
+        <v>0.2305077708506661</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0.2071952920335971</v>
+      </c>
+      <c r="L49" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="K49" s="5" t="n">
+      <c r="M49" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="L49" s="5" t="n">
+      <c r="N49" s="5" t="n">
         <v>0.8752</v>
       </c>
-      <c r="M49" s="5" t="n">
+      <c r="O49" s="5" t="n">
         <v>0.922</v>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="P49" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4167,25 +4423,31 @@
         <v>159</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="n">
+      <c r="J50" s="5" t="n">
+        <v>0.04243716720025748</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0.05545881975491462</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="n">
         <v>0.9046999999999999</v>
       </c>
-      <c r="M50" s="5" t="n">
+      <c r="O50" s="5" t="n">
         <v>0.9226</v>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="P50" s="5" t="n">
         <v>0.9214</v>
       </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="6" t="inlineStr"/>
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4223,25 +4485,31 @@
         <v>84.8</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="n">
+      <c r="J51" s="5" t="n">
+        <v>0.1040645720677824</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0.1371023035528832</v>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="n">
         <v>0.9182</v>
       </c>
-      <c r="M51" s="5" t="n">
+      <c r="O51" s="5" t="n">
         <v>0.9355</v>
       </c>
-      <c r="N51" s="5" t="n">
+      <c r="P51" s="5" t="n">
         <v>0.9349</v>
       </c>
-      <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="6" t="inlineStr"/>
       <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4279,25 +4547,31 @@
         <v>113.18</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="n">
+      <c r="J52" s="5" t="n">
+        <v>0.006039051040345522</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0.01443946864179979</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="n">
         <v>0.9344</v>
       </c>
-      <c r="M52" s="5" t="n">
+      <c r="O52" s="5" t="n">
         <v>0.9557</v>
       </c>
-      <c r="N52" s="5" t="n">
+      <c r="P52" s="5" t="n">
         <v>0.958</v>
       </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="6" t="inlineStr"/>
       <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="6" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4335,25 +4609,31 @@
         <v>113.19</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="n">
+      <c r="J53" s="5" t="n">
+        <v>0.02140267904180271</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.02661806541842593</v>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="n">
         <v>0.9518</v>
       </c>
-      <c r="M53" s="5" t="n">
+      <c r="O53" s="5" t="n">
         <v>0.9638</v>
       </c>
-      <c r="N53" s="5" t="n">
+      <c r="P53" s="5" t="n">
         <v>0.9544</v>
       </c>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="6" t="inlineStr"/>
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4393,23 +4673,25 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="n">
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="n">
         <v>0.9467</v>
       </c>
-      <c r="M54" s="5" t="n">
+      <c r="O54" s="5" t="n">
         <v>0.9649</v>
       </c>
-      <c r="N54" s="5" t="n">
+      <c r="P54" s="5" t="n">
         <v>0.9645</v>
       </c>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="6" t="inlineStr"/>
       <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="6" t="inlineStr"/>
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4447,25 +4729,31 @@
         <v>226</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="n">
+      <c r="J55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.004724844204588741</v>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="n">
         <v>0.9495</v>
       </c>
-      <c r="M55" s="5" t="n">
+      <c r="O55" s="5" t="n">
         <v>0.9628</v>
       </c>
-      <c r="N55" s="5" t="n">
+      <c r="P55" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="O55" s="6" t="inlineStr"/>
-      <c r="P55" s="6" t="inlineStr"/>
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="6" t="inlineStr"/>
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4503,25 +4791,31 @@
         <v>96.04000000000001</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="n">
+      <c r="J56" s="5" t="n">
+        <v>0.005091820276778458</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.0348272517253635</v>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="n">
         <v>0.9512</v>
       </c>
-      <c r="M56" s="5" t="n">
+      <c r="O56" s="5" t="n">
         <v>0.9644</v>
       </c>
-      <c r="N56" s="5" t="n">
+      <c r="P56" s="5" t="n">
         <v>0.9619</v>
       </c>
-      <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="6" t="inlineStr"/>
       <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="6" t="inlineStr"/>
       <c r="S56" s="6" t="inlineStr"/>
       <c r="T56" s="6" t="inlineStr"/>
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4559,25 +4853,31 @@
         <v>57</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="n">
+      <c r="J57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.04302205984473428</v>
+      </c>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="n">
         <v>0.9588</v>
       </c>
-      <c r="M57" s="5" t="n">
+      <c r="O57" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="N57" s="5" t="n">
+      <c r="P57" s="5" t="n">
         <v>0.9615</v>
       </c>
-      <c r="O57" s="6" t="inlineStr"/>
-      <c r="P57" s="6" t="inlineStr"/>
       <c r="Q57" s="6" t="inlineStr"/>
       <c r="R57" s="6" t="inlineStr"/>
       <c r="S57" s="6" t="inlineStr"/>
       <c r="T57" s="6" t="inlineStr"/>
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4615,25 +4915,31 @@
         <v>141</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="n">
+      <c r="J58" s="5" t="n">
+        <v>0.01096445117417066</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.03115483200409874</v>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="n">
         <v>0.928</v>
       </c>
-      <c r="M58" s="5" t="n">
+      <c r="O58" s="5" t="n">
         <v>0.9409</v>
       </c>
-      <c r="N58" s="5" t="n">
+      <c r="P58" s="5" t="n">
         <v>0.9276</v>
       </c>
-      <c r="O58" s="6" t="inlineStr"/>
-      <c r="P58" s="6" t="inlineStr"/>
       <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="6" t="inlineStr"/>
       <c r="S58" s="6" t="inlineStr"/>
       <c r="T58" s="6" t="inlineStr"/>
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
+      <c r="X58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4673,23 +4979,25 @@
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="n">
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="n">
         <v>0.9317</v>
       </c>
-      <c r="M59" s="5" t="n">
+      <c r="O59" s="5" t="n">
         <v>0.9520999999999999</v>
       </c>
-      <c r="N59" s="5" t="n">
+      <c r="P59" s="5" t="n">
         <v>0.9483</v>
       </c>
-      <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="6" t="inlineStr"/>
       <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="6" t="inlineStr"/>
       <c r="S59" s="6" t="inlineStr"/>
       <c r="T59" s="6" t="inlineStr"/>
       <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
+      <c r="X59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4727,25 +5035,31 @@
         <v>145</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="n">
+      <c r="J60" s="5" t="n">
+        <v>0.02821751962877717</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0.05196807492452316</v>
+      </c>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="n">
         <v>1.0205</v>
       </c>
-      <c r="M60" s="5" t="n">
+      <c r="O60" s="5" t="n">
         <v>1.0278</v>
       </c>
-      <c r="N60" s="5" t="n">
+      <c r="P60" s="5" t="n">
         <v>1.0041</v>
       </c>
-      <c r="O60" s="6" t="inlineStr"/>
-      <c r="P60" s="6" t="inlineStr"/>
       <c r="Q60" s="6" t="inlineStr"/>
       <c r="R60" s="6" t="inlineStr"/>
       <c r="S60" s="6" t="inlineStr"/>
       <c r="T60" s="6" t="inlineStr"/>
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
+      <c r="X60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4783,25 +5097,31 @@
         <v>165</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="n">
+      <c r="J61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0.01549209369771554</v>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="n">
         <v>0.9498</v>
       </c>
-      <c r="M61" s="5" t="n">
+      <c r="O61" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="N61" s="5" t="n">
+      <c r="P61" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="O61" s="6" t="inlineStr"/>
-      <c r="P61" s="6" t="inlineStr"/>
       <c r="Q61" s="6" t="inlineStr"/>
       <c r="R61" s="6" t="inlineStr"/>
       <c r="S61" s="6" t="inlineStr"/>
       <c r="T61" s="6" t="inlineStr"/>
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4839,25 +5159,31 @@
         <v>110</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="n">
+      <c r="J62" s="5" t="n">
+        <v>0.0152698174121777</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0.05647674886976661</v>
+      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="n">
         <v>0.9498</v>
       </c>
-      <c r="M62" s="5" t="n">
+      <c r="O62" s="5" t="n">
         <v>0.962</v>
       </c>
-      <c r="N62" s="5" t="n">
+      <c r="P62" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="6" t="inlineStr"/>
       <c r="Q62" s="6" t="inlineStr"/>
       <c r="R62" s="6" t="inlineStr"/>
       <c r="S62" s="6" t="inlineStr"/>
       <c r="T62" s="6" t="inlineStr"/>
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
+      <c r="X62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4895,25 +5221,31 @@
         <v>46.5</v>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="n">
+      <c r="J63" s="5" t="n">
+        <v>0.02413402691172006</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.01801957715632962</v>
+      </c>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="n">
         <v>0.9317</v>
       </c>
-      <c r="M63" s="5" t="n">
+      <c r="O63" s="5" t="n">
         <v>0.9520999999999999</v>
       </c>
-      <c r="N63" s="5" t="n">
+      <c r="P63" s="5" t="n">
         <v>0.9483</v>
       </c>
-      <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="6" t="inlineStr"/>
       <c r="Q63" s="6" t="inlineStr"/>
       <c r="R63" s="6" t="inlineStr"/>
       <c r="S63" s="6" t="inlineStr"/>
       <c r="T63" s="6" t="inlineStr"/>
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
+      <c r="X63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4951,25 +5283,31 @@
         <v>396</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="5" t="inlineStr"/>
-      <c r="L64" s="5" t="n">
+      <c r="J64" s="5" t="n">
+        <v>0.008069608842382725</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0.01353835130051628</v>
+      </c>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="n">
         <v>0.9427</v>
       </c>
-      <c r="M64" s="5" t="n">
+      <c r="O64" s="5" t="n">
         <v>0.9595</v>
       </c>
-      <c r="N64" s="5" t="n">
+      <c r="P64" s="5" t="n">
         <v>0.9578</v>
       </c>
-      <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="6" t="inlineStr"/>
       <c r="Q64" s="6" t="inlineStr"/>
       <c r="R64" s="6" t="inlineStr"/>
       <c r="S64" s="6" t="inlineStr"/>
       <c r="T64" s="6" t="inlineStr"/>
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
+      <c r="X64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5007,25 +5345,31 @@
         <v>270</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="n">
+      <c r="J65" s="5" t="n">
+        <v>0.004799051310686364</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>0.005648149462149199</v>
+      </c>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="n">
         <v>0.9012</v>
       </c>
-      <c r="M65" s="5" t="n">
+      <c r="O65" s="5" t="n">
         <v>0.8558</v>
       </c>
-      <c r="N65" s="5" t="n">
+      <c r="P65" s="5" t="n">
         <v>0.8683999999999999</v>
       </c>
-      <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="6" t="inlineStr"/>
       <c r="Q65" s="6" t="inlineStr"/>
       <c r="R65" s="6" t="inlineStr"/>
       <c r="S65" s="6" t="inlineStr"/>
       <c r="T65" s="6" t="inlineStr"/>
       <c r="U65" s="6" t="inlineStr"/>
       <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
+      <c r="X65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5063,25 +5407,31 @@
         <v>198.94</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="n">
+      <c r="J66" s="5" t="n">
+        <v>0.03591177586380856</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.06550375398343611</v>
+      </c>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="n">
         <v>0.805</v>
       </c>
-      <c r="M66" s="5" t="n">
+      <c r="O66" s="5" t="n">
         <v>0.8627</v>
       </c>
-      <c r="N66" s="5" t="n">
+      <c r="P66" s="5" t="n">
         <v>0.8871</v>
       </c>
-      <c r="O66" s="6" t="inlineStr"/>
-      <c r="P66" s="6" t="inlineStr"/>
       <c r="Q66" s="6" t="inlineStr"/>
       <c r="R66" s="6" t="inlineStr"/>
       <c r="S66" s="6" t="inlineStr"/>
       <c r="T66" s="6" t="inlineStr"/>
       <c r="U66" s="6" t="inlineStr"/>
       <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
+      <c r="X66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5119,25 +5469,31 @@
         <v>106.8</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="n">
+      <c r="J67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="n">
         <v>1.0088</v>
       </c>
-      <c r="M67" s="5" t="n">
+      <c r="O67" s="5" t="n">
         <v>0.9971</v>
       </c>
-      <c r="N67" s="5" t="n">
+      <c r="P67" s="5" t="n">
         <v>1.0006</v>
       </c>
-      <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="6" t="inlineStr"/>
       <c r="Q67" s="6" t="inlineStr"/>
       <c r="R67" s="6" t="inlineStr"/>
       <c r="S67" s="6" t="inlineStr"/>
       <c r="T67" s="6" t="inlineStr"/>
       <c r="U67" s="6" t="inlineStr"/>
       <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
+      <c r="X67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5175,25 +5531,31 @@
         <v>175</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="5" t="inlineStr"/>
-      <c r="L68" s="5" t="n">
+      <c r="J68" s="5" t="n">
+        <v>0.02932844669074952</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>0.05790697714739124</v>
+      </c>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="n">
         <v>0.8453000000000001</v>
       </c>
-      <c r="M68" s="5" t="n">
+      <c r="O68" s="5" t="n">
         <v>0.8149</v>
       </c>
-      <c r="N68" s="5" t="n">
+      <c r="P68" s="5" t="n">
         <v>0.8286</v>
       </c>
-      <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="6" t="inlineStr"/>
       <c r="Q68" s="6" t="inlineStr"/>
       <c r="R68" s="6" t="inlineStr"/>
       <c r="S68" s="6" t="inlineStr"/>
       <c r="T68" s="6" t="inlineStr"/>
       <c r="U68" s="6" t="inlineStr"/>
       <c r="V68" s="6" t="inlineStr"/>
+      <c r="W68" s="6" t="inlineStr"/>
+      <c r="X68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5231,25 +5593,31 @@
         <v>48.3</v>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="5" t="inlineStr"/>
-      <c r="L69" s="5" t="n">
+      <c r="J69" s="5" t="n">
+        <v>0.01613384681029095</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0.03042207487870752</v>
+      </c>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="n">
         <v>0.9467</v>
       </c>
-      <c r="M69" s="5" t="n">
+      <c r="O69" s="5" t="n">
         <v>0.9649</v>
       </c>
-      <c r="N69" s="5" t="n">
+      <c r="P69" s="5" t="n">
         <v>0.9645</v>
       </c>
-      <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="6" t="inlineStr"/>
       <c r="Q69" s="6" t="inlineStr"/>
       <c r="R69" s="6" t="inlineStr"/>
       <c r="S69" s="6" t="inlineStr"/>
       <c r="T69" s="6" t="inlineStr"/>
       <c r="U69" s="6" t="inlineStr"/>
       <c r="V69" s="6" t="inlineStr"/>
+      <c r="W69" s="6" t="inlineStr"/>
+      <c r="X69" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5262,7 +5630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U69"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5286,6 +5654,8 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5316,80 +5686,90 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY1_LABEL</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY2_LABEL</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_FY3_LABEL</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>ISP_CURTAILMENT_AVG</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY1_LABEL</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY2_LABEL</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_FY3_LABEL</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
         </is>
@@ -5416,25 +5796,23 @@
         <v>0.8245</v>
       </c>
       <c r="F2" s="5" t="n">
+        <v>0.05408598823176547</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.1498933489306341</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="I2" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L2" s="5" t="n">
@@ -5442,37 +5820,45 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="n">
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="n">
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="n">
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -5497,63 +5883,69 @@
         <v>0.9235</v>
       </c>
       <c r="F3" s="5" t="n">
+        <v>0.05478264603755456</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.1357018019333979</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="n">
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="n">
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="Q3" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="n">
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="n">
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="n">
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -5578,25 +5970,23 @@
         <v>0.869</v>
       </c>
       <c r="F4" s="5" t="n">
+        <v>0.1440247773689721</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.1299222960127742</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L4" s="5" t="n">
@@ -5604,37 +5994,45 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="n">
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="n">
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="n">
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -5659,63 +6057,69 @@
         <v>0.8405</v>
       </c>
       <c r="F5" s="5" t="n">
+        <v>0.1211386533906305</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.156935340089925</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>0.399270575823056</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>0.017550018083952</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="n">
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="n">
         <v>0.06999999999999999</v>
       </c>
     </row>
@@ -5742,43 +6146,45 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -5801,49 +6207,55 @@
         <v>0.825</v>
       </c>
       <c r="F7" s="5" t="n">
+        <v>0.03269498787171465</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.02926126425553777</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>0.0107432723897736</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -5866,63 +6278,69 @@
         <v>0.8778</v>
       </c>
       <c r="F8" s="5" t="n">
+        <v>0.09614342553807431</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.08192117087777062</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>0.529503172508041</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>7.253613938629221e-05</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n">
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="Q8" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="n">
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="n">
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="n">
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -5947,45 +6365,49 @@
         <v>0.8853</v>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -6008,49 +6430,55 @@
         <v>0.8395</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>0.06953767632819552</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.0882066342370772</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>0.0107432723897736</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr"/>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S10" s="5" t="inlineStr"/>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -6073,49 +6501,55 @@
         <v>0.8387</v>
       </c>
       <c r="F11" s="5" t="n">
+        <v>0.07039079639714096</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.08061793088892344</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>0.7032826997896851</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>0.264676213474225</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -6138,43 +6572,45 @@
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr"/>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="5" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr"/>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -6197,63 +6633,69 @@
         <v>0.8827</v>
       </c>
       <c r="F13" s="5" t="n">
+        <v>0.138756180474872</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.3633793594193425</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="n">
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="Q13" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="n">
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="n">
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n">
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -6277,50 +6719,52 @@
       <c r="E14" s="5" t="n">
         <v>0.8493000000000001</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>0.0107432723897736</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr"/>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -6343,49 +6787,55 @@
         <v>0.9605</v>
       </c>
       <c r="F15" s="5" t="n">
+        <v>0.03485234997163289</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.1455688224294164</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>0.165388664850326</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>0.000681438300925263</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="5" t="inlineStr"/>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr"/>
       <c r="Q15" s="5" t="inlineStr"/>
       <c r="R15" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S15" s="5" t="inlineStr"/>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -6408,25 +6858,23 @@
         <v>0.8473000000000001</v>
       </c>
       <c r="F16" s="5" t="n">
+        <v>0.1353701649733416</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.1888177292264882</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>0.903607825126104</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>0.900375357730696</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0.01</v>
-      </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L16" s="5" t="n">
@@ -6434,37 +6882,45 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N16" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>0.006666666666666667</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="Q16" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="n">
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="n">
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="n">
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="n">
         <v>0.07666666666666667</v>
       </c>
     </row>
@@ -6489,49 +6945,55 @@
         <v>0.848</v>
       </c>
       <c r="F17" s="5" t="n">
+        <v>0.1441759394227755</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.3082526071352186</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0.0107432723897736</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr"/>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr"/>
-      <c r="O17" s="5" t="inlineStr"/>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr"/>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -6554,49 +7016,55 @@
         <v>0.8823</v>
       </c>
       <c r="F18" s="5" t="n">
+        <v>0.07290536050268626</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.1189868785607631</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>0.886109380719023</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr"/>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr"/>
       <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr"/>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -6619,25 +7087,23 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F19" s="5" t="n">
+        <v>0.1624878107170906</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.2969960740318008</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L19" s="5" t="n">
@@ -6645,37 +7111,45 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="n">
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="n">
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n">
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -6700,63 +7174,69 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="F20" s="5" t="n">
+        <v>0.1329559142410704</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.2548659571637795</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="I20" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="Q20" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="n">
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -6781,63 +7261,69 @@
         <v>0.8143</v>
       </c>
       <c r="F21" s="5" t="n">
+        <v>0.1373179274132644</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.2539757919262627</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="I21" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="J21" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="n">
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="n">
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="Q21" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="n">
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="n">
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n">
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -6862,63 +7348,69 @@
         <v>0.9397</v>
       </c>
       <c r="F22" s="5" t="n">
+        <v>0.5229812164970579</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.6709166872938147</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="J22" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="n">
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n">
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="n">
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="Q22" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q22" s="5" t="n">
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="n">
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="n">
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -6943,63 +7435,69 @@
         <v>0.8702</v>
       </c>
       <c r="F23" s="5" t="n">
+        <v>0.007190464584342027</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.07108174352041219</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="I23" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="J23" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="n">
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n">
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="n">
         <v>0.24</v>
       </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="n">
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="Q23" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="n">
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="n">
         <v>0.26</v>
       </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="n">
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="n">
         <v>0.34</v>
       </c>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="n">
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -7024,63 +7522,69 @@
         <v>0.9517</v>
       </c>
       <c r="F24" s="5" t="n">
+        <v>0.5764125048753213</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.6755707391955864</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="I24" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="J24" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="n">
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n">
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="n">
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="Q24" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="n">
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="n">
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="n">
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -7105,25 +7609,23 @@
         <v>0.8541</v>
       </c>
       <c r="F25" s="5" t="n">
+        <v>0.01188361985022102</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.001815619300523097</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>0.188257195450457</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="I25" s="5" t="n">
         <v>0.0686562187806459</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>0.01</v>
-      </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L25" s="5" t="n">
@@ -7131,37 +7633,45 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N25" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="n">
         <v>0.006666666666666667</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="Q25" s="5" t="n">
         <v>0.04</v>
       </c>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="n">
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="n">
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="n">
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="n">
         <v>0.07666666666666667</v>
       </c>
     </row>
@@ -7188,43 +7698,45 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
       <c r="Q26" s="5" t="inlineStr"/>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7246,50 +7758,52 @@
       <c r="E27" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>0.0670248501388058</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -7312,63 +7826,69 @@
         <v>0.9258999999999999</v>
       </c>
       <c r="F28" s="5" t="n">
+        <v>0.03231345345515402</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.07990508599190627</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="I28" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="J28" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="n">
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="n">
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="n">
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="n">
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="n">
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -7393,63 +7913,69 @@
         <v>0.8943</v>
       </c>
       <c r="F29" s="5" t="n">
+        <v>0.09252848872869046</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.139740603518281</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="I29" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="J29" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="n">
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="n">
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="n">
         <v>0.24</v>
       </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="n">
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="Q29" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="n">
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="n">
         <v>0.26</v>
       </c>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="n">
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="n">
         <v>0.34</v>
       </c>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="n">
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -7474,63 +8000,69 @@
         <v>0.8943</v>
       </c>
       <c r="F30" s="5" t="n">
+        <v>0.09865070018729849</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.1267494122393782</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="I30" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="J30" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="n">
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n">
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="n">
         <v>0.24</v>
       </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="Q30" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="n">
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="n">
         <v>0.26</v>
       </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="n">
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="n">
         <v>0.34</v>
       </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="n">
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -7555,63 +8087,69 @@
         <v>0.9698</v>
       </c>
       <c r="F31" s="5" t="n">
+        <v>0.02789950205429714</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.03926636218841828</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="I31" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="J31" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="n">
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n">
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="n">
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="Q31" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q31" s="5" t="n">
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="n">
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="n">
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -7636,49 +8174,55 @@
         <v>0.8827</v>
       </c>
       <c r="F32" s="5" t="n">
+        <v>0.1275049435515178</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.3039969269602842</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="I32" s="5" t="n">
         <v>0.886109380719023</v>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr"/>
       <c r="Q32" s="5" t="inlineStr"/>
       <c r="R32" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -7701,43 +8245,45 @@
       <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -7762,43 +8308,45 @@
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
       <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr"/>
       <c r="T34" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7821,63 +8369,69 @@
         <v>0.8098</v>
       </c>
       <c r="F35" s="5" t="n">
+        <v>0.1153540312661219</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.1173458509370597</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="I35" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="J35" s="5" t="n">
         <v>0.11</v>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="n">
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n">
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="n">
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="Q35" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q35" s="5" t="n">
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="n">
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="n">
         <v>0.09</v>
       </c>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="n">
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -7902,25 +8456,23 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F36" s="5" t="n">
+        <v>0.1912183081095272</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.2595859755929798</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>0.1571570475144</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="I36" s="5" t="n">
         <v>0.0362161714591237</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L36" s="5" t="n">
@@ -7928,37 +8480,45 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q36" s="5" t="n">
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="n">
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="n">
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -7982,50 +8542,52 @@
       <c r="E37" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
         <v>0.167592623869037</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>0.000643212863569608</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
       <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -8047,64 +8609,68 @@
       <c r="E38" s="5" t="n">
         <v>0.9421</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="n">
+        <v>0.1421915117897189</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="I38" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="J38" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="n">
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="n">
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="n">
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O38" s="5" t="n">
+      <c r="Q38" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q38" s="5" t="n">
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="n">
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="n">
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -8128,64 +8694,68 @@
       <c r="E39" s="5" t="n">
         <v>0.9421</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="n">
+        <v>0.1466186570287763</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="I39" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="J39" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="n">
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n">
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="n">
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="Q39" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q39" s="5" t="n">
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="n">
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="n">
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -8210,63 +8780,69 @@
         <v>0.9054</v>
       </c>
       <c r="F40" s="5" t="n">
+        <v>0.1345570232002854</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.1216265245384226</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="I40" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="J40" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="n">
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n">
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="n">
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="Q40" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q40" s="5" t="n">
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="n">
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="n">
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -8291,25 +8867,23 @@
         <v>0.8686</v>
       </c>
       <c r="F41" s="5" t="n">
+        <v>0.1713544037663096</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.2654827427546417</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="I41" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
@@ -8317,37 +8891,45 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="P41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q41" s="5" t="n">
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="n">
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="n">
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="n">
         <v>0.03333333333333333</v>
       </c>
     </row>
@@ -8371,50 +8953,54 @@
       <c r="E42" s="5" t="n">
         <v>0.8796</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="n">
+        <v>0.1015077616127097</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="I42" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
       <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8436,50 +9022,54 @@
       <c r="E43" s="5" t="n">
         <v>0.8783</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="n">
+        <v>0.08481628251174367</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="I43" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
       <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8502,63 +9092,69 @@
         <v>0.9364</v>
       </c>
       <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.06566494744533402</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="I44" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="J44" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="n">
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="n">
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="n">
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="Q44" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="n">
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="n">
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="n">
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -8583,63 +9179,69 @@
         <v>0.9258999999999999</v>
       </c>
       <c r="F45" s="5" t="n">
+        <v>0.03240949212773014</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.03166342025536539</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="I45" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="J45" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="n">
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
         <v>0.12</v>
       </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="n">
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="n">
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="n">
         <v>0.1433333333333333</v>
       </c>
-      <c r="O45" s="5" t="n">
+      <c r="Q45" s="5" t="n">
         <v>0.21</v>
       </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="n">
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="n">
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="n">
         <v>0.22</v>
       </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="n">
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="n">
         <v>0.2066666666666667</v>
       </c>
     </row>
@@ -8664,49 +9266,55 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F46" s="5" t="n">
+        <v>0.1526525054987787</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.1992808636220385</v>
+      </c>
+      <c r="H46" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
-      <c r="G46" s="5" t="n">
+      <c r="I46" s="5" t="n">
         <v>0.0107432723897736</v>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
       <c r="Q46" s="5" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8729,63 +9337,69 @@
         <v>0.8286</v>
       </c>
       <c r="F47" s="5" t="n">
+        <v>0.06560284749189083</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.06534439203754416</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="I47" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="J47" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="n">
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="n">
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="n">
         <v>0.24</v>
       </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="n">
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="n">
         <v>0.1633333333333333</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="Q47" s="5" t="n">
         <v>0.16</v>
       </c>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="n">
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="n">
         <v>0.26</v>
       </c>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="n">
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="n">
         <v>0.34</v>
       </c>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="n">
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="n">
         <v>0.2533333333333334</v>
       </c>
     </row>
@@ -8809,50 +9423,54 @@
       <c r="E48" s="5" t="n">
         <v>0.9548</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="n">
+        <v>0.2050867232572048</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <v>0.158699742317549</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="I48" s="5" t="n">
         <v>0.000581408571101005</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
       <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S48" s="5" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8875,49 +9493,55 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F49" s="5" t="n">
+        <v>0.2305077708506661</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.2071952920335971</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="I49" s="5" t="n">
         <v>0.00631707880200049</v>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8939,46 +9563,52 @@
       <c r="E50" s="5" t="n">
         <v>0.9214</v>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>0.04243716720025748</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.05545881975491462</v>
+      </c>
       <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr"/>
       <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S50" s="5" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -9000,46 +9630,52 @@
       <c r="E51" s="5" t="n">
         <v>0.9349</v>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="n">
+        <v>0.1040645720677824</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.1371023035528832</v>
+      </c>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S51" s="5" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -9061,46 +9697,52 @@
       <c r="E52" s="5" t="n">
         <v>0.958</v>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>0.006039051040345522</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.01443946864179979</v>
+      </c>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr"/>
       <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S52" s="5" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -9122,46 +9764,52 @@
       <c r="E53" s="5" t="n">
         <v>0.9544</v>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="n">
+        <v>0.02140267904180271</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.02661806541842593</v>
+      </c>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr"/>
       <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S53" s="5" t="inlineStr"/>
       <c r="T53" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -9186,43 +9834,45 @@
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
       <c r="Q54" s="5" t="inlineStr"/>
       <c r="R54" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S54" s="5" t="inlineStr"/>
       <c r="T54" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -9244,46 +9894,52 @@
       <c r="E55" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.004724844204588741</v>
+      </c>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr"/>
       <c r="Q55" s="5" t="inlineStr"/>
       <c r="R55" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S55" s="5" t="inlineStr"/>
       <c r="T55" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -9305,46 +9961,52 @@
       <c r="E56" s="5" t="n">
         <v>0.9619</v>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="n">
+        <v>0.005091820276778458</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0348272517253635</v>
+      </c>
       <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="5" t="inlineStr"/>
-      <c r="P56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr"/>
       <c r="Q56" s="5" t="inlineStr"/>
       <c r="R56" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S56" s="5" t="inlineStr"/>
       <c r="T56" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U56" s="5" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -9366,46 +10028,52 @@
       <c r="E57" s="5" t="n">
         <v>0.9615</v>
       </c>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.04302205984473428</v>
+      </c>
       <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr"/>
       <c r="Q57" s="5" t="inlineStr"/>
       <c r="R57" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S57" s="5" t="inlineStr"/>
       <c r="T57" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U57" s="5" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -9427,46 +10095,52 @@
       <c r="E58" s="5" t="n">
         <v>0.9276</v>
       </c>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="n">
+        <v>0.01096445117417066</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.03115483200409874</v>
+      </c>
       <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr"/>
-      <c r="P58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr"/>
       <c r="Q58" s="5" t="inlineStr"/>
       <c r="R58" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S58" s="5" t="inlineStr"/>
       <c r="T58" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U58" s="5" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -9491,43 +10165,45 @@
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="5" t="inlineStr"/>
-      <c r="P59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr"/>
       <c r="Q59" s="5" t="inlineStr"/>
       <c r="R59" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S59" s="5" t="inlineStr"/>
       <c r="T59" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -9549,46 +10225,52 @@
       <c r="E60" s="5" t="n">
         <v>1.0041</v>
       </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="n">
+        <v>0.02821751962877717</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.05196807492452316</v>
+      </c>
       <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="5" t="inlineStr"/>
-      <c r="P60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr"/>
       <c r="Q60" s="5" t="inlineStr"/>
       <c r="R60" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S60" s="5" t="inlineStr"/>
       <c r="T60" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U60" s="5" t="inlineStr"/>
+      <c r="V60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -9610,46 +10292,52 @@
       <c r="E61" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.01549209369771554</v>
+      </c>
       <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="5" t="inlineStr"/>
-      <c r="P61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr"/>
       <c r="Q61" s="5" t="inlineStr"/>
       <c r="R61" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S61" s="5" t="inlineStr"/>
       <c r="T61" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -9671,46 +10359,52 @@
       <c r="E62" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="n">
+        <v>0.0152698174121777</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.05647674886976661</v>
+      </c>
       <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
-      <c r="O62" s="5" t="inlineStr"/>
-      <c r="P62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr"/>
       <c r="Q62" s="5" t="inlineStr"/>
       <c r="R62" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S62" s="5" t="inlineStr"/>
       <c r="T62" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U62" s="5" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -9732,46 +10426,52 @@
       <c r="E63" s="5" t="n">
         <v>0.9483</v>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="n">
+        <v>0.02413402691172006</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.01801957715632962</v>
+      </c>
       <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="5" t="inlineStr"/>
-      <c r="P63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="inlineStr"/>
       <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S63" s="5" t="inlineStr"/>
       <c r="T63" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U63" s="5" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -9793,46 +10493,52 @@
       <c r="E64" s="5" t="n">
         <v>0.9578</v>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="n">
+        <v>0.008069608842382725</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.01353835130051628</v>
+      </c>
       <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="5" t="inlineStr"/>
-      <c r="P64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr"/>
       <c r="Q64" s="5" t="inlineStr"/>
       <c r="R64" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S64" s="5" t="inlineStr"/>
       <c r="T64" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U64" s="5" t="inlineStr"/>
+      <c r="V64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -9854,46 +10560,52 @@
       <c r="E65" s="5" t="n">
         <v>0.8683999999999999</v>
       </c>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="n">
+        <v>0.004799051310686364</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.005648149462149199</v>
+      </c>
       <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
-      <c r="O65" s="5" t="inlineStr"/>
-      <c r="P65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr"/>
       <c r="Q65" s="5" t="inlineStr"/>
       <c r="R65" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S65" s="5" t="inlineStr"/>
       <c r="T65" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U65" s="5" t="inlineStr"/>
+      <c r="V65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -9915,46 +10627,52 @@
       <c r="E66" s="5" t="n">
         <v>0.8871</v>
       </c>
-      <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="n">
+        <v>0.03591177586380856</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.06550375398343611</v>
+      </c>
       <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
-      <c r="O66" s="5" t="inlineStr"/>
-      <c r="P66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr"/>
       <c r="Q66" s="5" t="inlineStr"/>
       <c r="R66" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S66" s="5" t="inlineStr"/>
       <c r="T66" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U66" s="5" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -9976,46 +10694,52 @@
       <c r="E67" s="5" t="n">
         <v>1.0006</v>
       </c>
-      <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="5" t="inlineStr"/>
-      <c r="P67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr"/>
       <c r="Q67" s="5" t="inlineStr"/>
       <c r="R67" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S67" s="5" t="inlineStr"/>
       <c r="T67" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -10037,46 +10761,52 @@
       <c r="E68" s="5" t="n">
         <v>0.8286</v>
       </c>
-      <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="n">
+        <v>0.02932844669074952</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.05790697714739124</v>
+      </c>
       <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
-      <c r="O68" s="5" t="inlineStr"/>
-      <c r="P68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="inlineStr"/>
       <c r="Q68" s="5" t="inlineStr"/>
       <c r="R68" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S68" s="5" t="inlineStr"/>
       <c r="T68" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U68" s="5" t="inlineStr"/>
+      <c r="V68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -10098,46 +10828,52 @@
       <c r="E69" s="5" t="n">
         <v>0.9645</v>
       </c>
-      <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="n">
+        <v>0.01613384681029095</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.03042207487870752</v>
+      </c>
       <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
-      <c r="O69" s="5" t="inlineStr"/>
-      <c r="P69" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="inlineStr"/>
       <c r="Q69" s="5" t="inlineStr"/>
       <c r="R69" s="5" t="inlineStr">
         <is>
-          <t>26-27</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="S69" s="5" t="inlineStr"/>
       <c r="T69" s="5" t="inlineStr">
         <is>
-          <t>27-28</t>
+          <t>26-27</t>
         </is>
       </c>
       <c r="U69" s="5" t="inlineStr"/>
+      <c r="V69" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W69" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C69">
@@ -10368,6 +11104,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V69">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W69">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,9 +82,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,14 +472,6 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,46 +555,6 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curt FY3</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Curt Avg</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY1</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY2</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Offl FY3</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Offl Avg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -650,10 +599,10 @@
         <v>132</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.05408598823176547</v>
+        <v>0.0511</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.1498933489306341</v>
+        <v>0.1441</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -670,30 +619,6 @@
       <c r="P2" s="5" t="n">
         <v>0.8245</v>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V2" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W2" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X2" s="6" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -732,16 +657,16 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.05478264603755456</v>
+        <v>0.0521</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0.1357018019333979</v>
+        <v>0.128</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0.636442356808484</v>
@@ -758,30 +683,6 @@
       <c r="P3" s="5" t="n">
         <v>0.9235</v>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S3" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T3" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U3" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V3" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W3" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X3" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -826,10 +727,10 @@
         <v>132</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.1440247773689721</v>
+        <v>0.132</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.1299222960127742</v>
+        <v>0.123</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -846,30 +747,6 @@
       <c r="P4" s="5" t="n">
         <v>0.869</v>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V4" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X4" s="6" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -908,16 +785,16 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>53.76</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>22</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1211386533906305</v>
+        <v>0.115</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.156935340089925</v>
+        <v>0.1492</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.399270575823056</v>
@@ -933,30 +810,6 @@
       </c>
       <c r="P5" s="5" t="n">
         <v>0.8405</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="X5" s="6" t="n">
-        <v>0.06999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1008,14 +861,6 @@
       <c r="P6" s="5" t="n">
         <v>0.9961</v>
       </c>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="6" t="inlineStr"/>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="6" t="inlineStr"/>
-      <c r="V6" s="6" t="inlineStr"/>
-      <c r="W6" s="6" t="inlineStr"/>
-      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1054,16 +899,16 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>180</v>
+        <v>150.3</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.03269498787171465</v>
+        <v>0.0327</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.02926126425553777</v>
+        <v>0.0292</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>0.64186785726147</v>
@@ -1080,14 +925,6 @@
       <c r="P7" s="5" t="n">
         <v>0.825</v>
       </c>
-      <c r="Q7" s="6" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="6" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="6" t="inlineStr"/>
-      <c r="V7" s="6" t="inlineStr"/>
-      <c r="W7" s="6" t="inlineStr"/>
-      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1126,16 +963,16 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>36</v>
+        <v>36.01</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.09614342553807431</v>
+        <v>0.0862</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.08192117087777062</v>
+        <v>0.0799</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0.529503172508041</v>
@@ -1152,30 +989,6 @@
       <c r="P8" s="5" t="n">
         <v>0.8778</v>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T8" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U8" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V8" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W8" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1214,9 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="n">
@@ -1228,14 +1039,6 @@
       <c r="P9" s="5" t="n">
         <v>0.8853</v>
       </c>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr"/>
-      <c r="V9" s="6" t="inlineStr"/>
-      <c r="W9" s="6" t="inlineStr"/>
-      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1274,16 +1077,16 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>324</v>
+        <v>274.97</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.06953767632819552</v>
+        <v>0.0636</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.0882066342370772</v>
+        <v>0.0833</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.64186785726147</v>
@@ -1300,14 +1103,6 @@
       <c r="P10" s="5" t="n">
         <v>0.8395</v>
       </c>
-      <c r="Q10" s="6" t="inlineStr"/>
-      <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="6" t="inlineStr"/>
-      <c r="T10" s="6" t="inlineStr"/>
-      <c r="U10" s="6" t="inlineStr"/>
-      <c r="V10" s="6" t="inlineStr"/>
-      <c r="W10" s="6" t="inlineStr"/>
-      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1352,10 +1147,10 @@
         <v>132</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.07039079639714096</v>
+        <v>0.0643</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.08061793088892344</v>
+        <v>0.0762</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0.7032826997896851</v>
@@ -1372,14 +1167,6 @@
       <c r="P11" s="5" t="n">
         <v>0.8387</v>
       </c>
-      <c r="Q11" s="6" t="inlineStr"/>
-      <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="6" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr"/>
-      <c r="U11" s="6" t="inlineStr"/>
-      <c r="V11" s="6" t="inlineStr"/>
-      <c r="W11" s="6" t="inlineStr"/>
-      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1428,14 +1215,6 @@
       <c r="P12" s="5" t="n">
         <v>0.884</v>
       </c>
-      <c r="Q12" s="6" t="inlineStr"/>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="6" t="inlineStr"/>
-      <c r="T12" s="6" t="inlineStr"/>
-      <c r="U12" s="6" t="inlineStr"/>
-      <c r="V12" s="6" t="inlineStr"/>
-      <c r="W12" s="6" t="inlineStr"/>
-      <c r="X12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1474,16 +1253,16 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>85</v>
+        <v>69.75</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.138756180474872</v>
+        <v>0.132</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.3633793594193425</v>
+        <v>0.3285</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>0.87127903942823</v>
@@ -1500,30 +1279,6 @@
       <c r="P13" s="5" t="n">
         <v>0.8827</v>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T13" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U13" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V13" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W13" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X13" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1562,7 +1317,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>27.2</v>
+        <v>27.19</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>33</v>
@@ -1584,14 +1339,6 @@
       <c r="P14" s="5" t="n">
         <v>0.8493000000000001</v>
       </c>
-      <c r="Q14" s="6" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="6" t="inlineStr"/>
-      <c r="T14" s="6" t="inlineStr"/>
-      <c r="U14" s="6" t="inlineStr"/>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="6" t="inlineStr"/>
-      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1636,10 +1383,10 @@
         <v>330</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.03485234997163289</v>
+        <v>0.0328</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.1455688224294164</v>
+        <v>0.1353</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.165388664850326</v>
@@ -1656,14 +1403,6 @@
       <c r="P15" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="Q15" s="6" t="inlineStr"/>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="6" t="inlineStr"/>
-      <c r="T15" s="6" t="inlineStr"/>
-      <c r="U15" s="6" t="inlineStr"/>
-      <c r="V15" s="6" t="inlineStr"/>
-      <c r="W15" s="6" t="inlineStr"/>
-      <c r="X15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1702,16 +1441,16 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1353701649733416</v>
+        <v>0.1268</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.1888177292264882</v>
+        <v>0.1778</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.903607825126104</v>
@@ -1728,30 +1467,6 @@
       <c r="P16" s="5" t="n">
         <v>0.8473000000000001</v>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S16" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T16" s="6" t="n">
-        <v>0.006666666666666667</v>
-      </c>
-      <c r="U16" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V16" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W16" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="X16" s="6" t="n">
-        <v>0.07666666666666667</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1796,10 +1511,10 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1441759394227755</v>
+        <v>0.1304</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3082526071352186</v>
+        <v>0.2781</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.64186785726147</v>
@@ -1816,14 +1531,6 @@
       <c r="P17" s="5" t="n">
         <v>0.848</v>
       </c>
-      <c r="Q17" s="6" t="inlineStr"/>
-      <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="6" t="inlineStr"/>
-      <c r="T17" s="6" t="inlineStr"/>
-      <c r="U17" s="6" t="inlineStr"/>
-      <c r="V17" s="6" t="inlineStr"/>
-      <c r="W17" s="6" t="inlineStr"/>
-      <c r="X17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1868,10 +1575,10 @@
         <v>66</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.07290536050268626</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.1189868785607631</v>
+        <v>0.1147</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0.87127903942823</v>
@@ -1888,14 +1595,6 @@
       <c r="P18" s="5" t="n">
         <v>0.8823</v>
       </c>
-      <c r="Q18" s="6" t="inlineStr"/>
-      <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="6" t="inlineStr"/>
-      <c r="T18" s="6" t="inlineStr"/>
-      <c r="U18" s="6" t="inlineStr"/>
-      <c r="V18" s="6" t="inlineStr"/>
-      <c r="W18" s="6" t="inlineStr"/>
-      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1934,16 +1633,16 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>36</v>
+        <v>36.01</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.1624878107170906</v>
+        <v>0.1534</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.2969960740318008</v>
+        <v>0.2801</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -1960,30 +1659,6 @@
       <c r="P19" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V19" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W19" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X19" s="6" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2022,16 +1697,16 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>220</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.1329559142410704</v>
+        <v>0.1138</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.2548659571637795</v>
+        <v>0.2431</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.505349468159863</v>
@@ -2048,30 +1723,6 @@
       <c r="P20" s="5" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="X20" s="6" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2110,16 +1761,16 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>38</v>
+        <v>28.98</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>22</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1373179274132644</v>
+        <v>0.1244</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.2539757919262627</v>
+        <v>0.2403</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>0.505349468159863</v>
@@ -2136,30 +1787,6 @@
       <c r="P21" s="5" t="n">
         <v>0.8143</v>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="X21" s="6" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2204,10 +1831,10 @@
         <v>132</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.5229812164970579</v>
+        <v>0.4514</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.6709166872938147</v>
+        <v>0.5511</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0.919931770355409</v>
@@ -2224,30 +1851,6 @@
       <c r="P22" s="5" t="n">
         <v>0.9397</v>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S22" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T22" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U22" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V22" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W22" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X22" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2292,10 +1895,10 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.007190464584342027</v>
+        <v>0.0075</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.07108174352041219</v>
+        <v>0.0614</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0.231026075027885</v>
@@ -2312,30 +1915,6 @@
       <c r="P23" s="5" t="n">
         <v>0.8702</v>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T23" s="6" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="U23" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V23" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="W23" s="6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="X23" s="6" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2374,16 +1953,16 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>36</v>
+        <v>36.08</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.5764125048753213</v>
+        <v>0.488</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.6755707391955864</v>
+        <v>0.5639</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0.919931770355409</v>
@@ -2400,30 +1979,6 @@
       <c r="P24" s="5" t="n">
         <v>0.9517</v>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T24" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U24" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V24" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W24" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X24" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2462,16 +2017,16 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>57.064</v>
+        <v>56</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.01188361985022102</v>
+        <v>0.012</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.001815619300523097</v>
+        <v>0.0089</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>0.188257195450457</v>
@@ -2487,30 +2042,6 @@
       </c>
       <c r="P25" s="5" t="n">
         <v>0.8541</v>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S25" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T25" s="6" t="n">
-        <v>0.006666666666666667</v>
-      </c>
-      <c r="U25" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="V25" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W25" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="X25" s="6" t="n">
-        <v>0.07666666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -2562,14 +2093,6 @@
       <c r="P26" s="5" t="n">
         <v>0.9799</v>
       </c>
-      <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr"/>
-      <c r="U26" s="6" t="inlineStr"/>
-      <c r="V26" s="6" t="inlineStr"/>
-      <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2608,7 +2131,7 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
         <v>132</v>
@@ -2630,14 +2153,6 @@
       <c r="P27" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr"/>
-      <c r="U27" s="6" t="inlineStr"/>
-      <c r="V27" s="6" t="inlineStr"/>
-      <c r="W27" s="6" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2676,16 +2191,16 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>132</v>
+        <v>104.64</v>
       </c>
       <c r="I28" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.03231345345515402</v>
+        <v>0.0332</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.07990508599190627</v>
+        <v>0.078</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0.15663609258386</v>
@@ -2702,30 +2217,6 @@
       <c r="P28" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S28" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T28" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U28" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V28" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W28" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X28" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2764,16 +2255,16 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.09252848872869046</v>
+        <v>0.0851</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.139740603518281</v>
+        <v>0.125</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>0.231026075027885</v>
@@ -2790,30 +2281,6 @@
       <c r="P29" s="5" t="n">
         <v>0.8943</v>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="S29" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T29" s="6" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="U29" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V29" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="W29" s="6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="X29" s="6" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2852,16 +2319,16 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="I30" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.09865070018729849</v>
+        <v>0.0885</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.1267494122393782</v>
+        <v>0.1153</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0.231026075027885</v>
@@ -2878,30 +2345,6 @@
       <c r="P30" s="5" t="n">
         <v>0.8943</v>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T30" s="6" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="U30" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V30" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="W30" s="6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="X30" s="6" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2940,16 +2383,16 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>102.141</v>
+        <v>102.03</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0.02789950205429714</v>
+        <v>0.0277</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.03926636218841828</v>
+        <v>0.0388</v>
       </c>
       <c r="L31" s="5" t="n">
         <v>0.15663609258386</v>
@@ -2966,30 +2409,6 @@
       <c r="P31" s="5" t="n">
         <v>0.9698</v>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T31" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U31" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V31" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W31" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X31" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3028,16 +2447,16 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>55</v>
+        <v>49.5</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.1275049435515178</v>
+        <v>0.123</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.3039969269602842</v>
+        <v>0.2694</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>0.87127903942823</v>
@@ -3054,14 +2473,6 @@
       <c r="P32" s="5" t="n">
         <v>0.8827</v>
       </c>
-      <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr"/>
-      <c r="V32" s="6" t="inlineStr"/>
-      <c r="W32" s="6" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3110,14 +2521,6 @@
       <c r="P33" s="5" t="n">
         <v>0.8863</v>
       </c>
-      <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3168,14 +2571,6 @@
       <c r="P34" s="5" t="n">
         <v>0.9656</v>
       </c>
-      <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3214,16 +2609,16 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>228</v>
+        <v>228.8</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>220</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.1153540312661219</v>
+        <v>0.1059</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.1173458509370597</v>
+        <v>0.1146</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>0.505349468159863</v>
@@ -3240,30 +2635,6 @@
       <c r="P35" s="5" t="n">
         <v>0.8098</v>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T35" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U35" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V35" s="6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W35" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="X35" s="6" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3302,16 +2673,16 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.1912183081095272</v>
+        <v>0.1766</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.2595859755929798</v>
+        <v>0.2365</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0.1571570475144</v>
@@ -3328,30 +2699,6 @@
       <c r="P36" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V36" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W36" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X36" s="6" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3390,7 +2737,7 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>132</v>
@@ -3412,14 +2759,6 @@
       <c r="P37" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr"/>
-      <c r="U37" s="6" t="inlineStr"/>
-      <c r="V37" s="6" t="inlineStr"/>
-      <c r="W37" s="6" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3458,15 +2797,13 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="n">
-        <v>0.1421915117897189</v>
-      </c>
+      <c r="K38" s="5" t="inlineStr"/>
       <c r="L38" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -3482,30 +2819,6 @@
       <c r="P38" s="5" t="n">
         <v>0.9421</v>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S38" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T38" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U38" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V38" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W38" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X38" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3544,15 +2857,13 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="n">
-        <v>0.1466186570287763</v>
-      </c>
+      <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -3568,30 +2879,6 @@
       <c r="P39" s="5" t="n">
         <v>0.9421</v>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S39" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T39" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U39" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V39" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W39" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X39" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3630,16 +2917,16 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.1345570232002854</v>
+        <v>0.1231</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.1216265245384226</v>
+        <v>0.1167</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0.15663609258386</v>
@@ -3656,30 +2943,6 @@
       <c r="P40" s="5" t="n">
         <v>0.9054</v>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U40" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V40" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W40" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X40" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3718,16 +2981,16 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>55</v>
+        <v>19.64</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>66</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.1713544037663096</v>
+        <v>0.1585</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.2654827427546417</v>
+        <v>0.2501</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -3744,30 +3007,6 @@
       <c r="P41" s="5" t="n">
         <v>0.8686</v>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V41" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W41" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X41" s="6" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3806,15 +3045,13 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>201.6</v>
+        <v>151.97</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="n">
-        <v>0.1015077616127097</v>
-      </c>
+      <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -3830,14 +3067,6 @@
       <c r="P42" s="5" t="n">
         <v>0.8796</v>
       </c>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3876,15 +3105,13 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>201.6</v>
+        <v>151.97</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="n">
-        <v>0.08481628251174367</v>
-      </c>
+      <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -3900,14 +3127,6 @@
       <c r="P43" s="5" t="n">
         <v>0.8783</v>
       </c>
-      <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
-      <c r="V43" s="6" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3946,16 +3165,14 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>436</v>
+        <v>436.8</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="n">
-        <v>0.06566494744533402</v>
+        <v>0.0616</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0.15663609258386</v>
@@ -3972,30 +3189,6 @@
       <c r="P44" s="5" t="n">
         <v>0.9364</v>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S44" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T44" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U44" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V44" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W44" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X44" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4034,16 +3227,16 @@
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>216</v>
+        <v>216.08</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0.03240949212773014</v>
+        <v>0.0315</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.03166342025536539</v>
+        <v>0.0306</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>0.15663609258386</v>
@@ -4060,30 +3253,6 @@
       <c r="P45" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="S45" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T45" s="6" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="U45" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="V45" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="W45" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X45" s="6" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4122,16 +3291,16 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>105</v>
+        <v>105.27</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0.1526525054987787</v>
+        <v>0.1433</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.1992808636220385</v>
+        <v>0.1883</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>0.64186785726147</v>
@@ -4148,14 +3317,6 @@
       <c r="P46" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4194,16 +3355,16 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>0.06560284749189083</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.06534439203754416</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>0.231026075027885</v>
@@ -4220,30 +3381,6 @@
       <c r="P47" s="5" t="n">
         <v>0.8286</v>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="S47" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T47" s="6" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="U47" s="6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="V47" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="W47" s="6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="X47" s="6" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4282,15 +3419,13 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="I48" s="2" t="n">
         <v>330</v>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="n">
-        <v>0.2050867232572048</v>
-      </c>
+      <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="n">
         <v>0.158699742317549</v>
       </c>
@@ -4306,14 +3441,6 @@
       <c r="P48" s="5" t="n">
         <v>0.9548</v>
       </c>
-      <c r="Q48" s="6" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4352,16 +3479,16 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>62</v>
+        <v>62.32</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>132</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>0.2305077708506661</v>
+        <v>0.2031</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.2071952920335971</v>
+        <v>0.1969</v>
       </c>
       <c r="L49" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -4378,14 +3505,6 @@
       <c r="P49" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="Q49" s="6" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4424,10 +3543,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.04243716720025748</v>
+        <v>0.042</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.05545881975491462</v>
+        <v>0.0528</v>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
@@ -4440,14 +3559,6 @@
       <c r="P50" s="5" t="n">
         <v>0.9214</v>
       </c>
-      <c r="Q50" s="6" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4486,10 +3597,10 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="5" t="n">
-        <v>0.1040645720677824</v>
+        <v>0.0983</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.1371023035528832</v>
+        <v>0.1308</v>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
@@ -4502,14 +3613,6 @@
       <c r="P51" s="5" t="n">
         <v>0.9349</v>
       </c>
-      <c r="Q51" s="6" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
-      <c r="V51" s="6" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4548,10 +3651,10 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="n">
-        <v>0.006039051040345522</v>
+        <v>0.006</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.01443946864179979</v>
+        <v>0.0143</v>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
@@ -4564,14 +3667,6 @@
       <c r="P52" s="5" t="n">
         <v>0.958</v>
       </c>
-      <c r="Q52" s="6" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4610,10 +3705,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.02140267904180271</v>
+        <v>0.0213</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.02661806541842593</v>
+        <v>0.0265</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
@@ -4626,14 +3721,6 @@
       <c r="P53" s="5" t="n">
         <v>0.9544</v>
       </c>
-      <c r="Q53" s="6" t="inlineStr"/>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="6" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4684,14 +3771,6 @@
       <c r="P54" s="5" t="n">
         <v>0.9645</v>
       </c>
-      <c r="Q54" s="6" t="inlineStr"/>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4730,10 +3809,10 @@
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="5" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.004724844204588741</v>
+        <v>0.0066</v>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
@@ -4746,14 +3825,6 @@
       <c r="P55" s="5" t="n">
         <v>0.9608</v>
       </c>
-      <c r="Q55" s="6" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr"/>
-      <c r="V55" s="6" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4791,12 +3862,8 @@
         <v>96.04000000000001</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="5" t="n">
-        <v>0.005091820276778458</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>0.0348272517253635</v>
-      </c>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="n">
@@ -4808,14 +3875,6 @@
       <c r="P56" s="5" t="n">
         <v>0.9619</v>
       </c>
-      <c r="Q56" s="6" t="inlineStr"/>
-      <c r="R56" s="6" t="inlineStr"/>
-      <c r="S56" s="6" t="inlineStr"/>
-      <c r="T56" s="6" t="inlineStr"/>
-      <c r="U56" s="6" t="inlineStr"/>
-      <c r="V56" s="6" t="inlineStr"/>
-      <c r="W56" s="6" t="inlineStr"/>
-      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4853,12 +3912,8 @@
         <v>57</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>0.04302205984473428</v>
-      </c>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="n">
@@ -4870,14 +3925,6 @@
       <c r="P57" s="5" t="n">
         <v>0.9615</v>
       </c>
-      <c r="Q57" s="6" t="inlineStr"/>
-      <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="6" t="inlineStr"/>
-      <c r="T57" s="6" t="inlineStr"/>
-      <c r="U57" s="6" t="inlineStr"/>
-      <c r="V57" s="6" t="inlineStr"/>
-      <c r="W57" s="6" t="inlineStr"/>
-      <c r="X57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4916,10 +3963,10 @@
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="5" t="n">
-        <v>0.01096445117417066</v>
+        <v>0.0109</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.03115483200409874</v>
+        <v>0.0298</v>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
@@ -4932,14 +3979,6 @@
       <c r="P58" s="5" t="n">
         <v>0.9276</v>
       </c>
-      <c r="Q58" s="6" t="inlineStr"/>
-      <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="6" t="inlineStr"/>
-      <c r="T58" s="6" t="inlineStr"/>
-      <c r="U58" s="6" t="inlineStr"/>
-      <c r="V58" s="6" t="inlineStr"/>
-      <c r="W58" s="6" t="inlineStr"/>
-      <c r="X58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4990,14 +4029,6 @@
       <c r="P59" s="5" t="n">
         <v>0.9483</v>
       </c>
-      <c r="Q59" s="6" t="inlineStr"/>
-      <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="6" t="inlineStr"/>
-      <c r="T59" s="6" t="inlineStr"/>
-      <c r="U59" s="6" t="inlineStr"/>
-      <c r="V59" s="6" t="inlineStr"/>
-      <c r="W59" s="6" t="inlineStr"/>
-      <c r="X59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5035,11 +4066,9 @@
         <v>145</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="5" t="n">
-        <v>0.02821751962877717</v>
-      </c>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="n">
-        <v>0.05196807492452316</v>
+        <v>0.0509</v>
       </c>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
@@ -5052,14 +4081,6 @@
       <c r="P60" s="5" t="n">
         <v>1.0041</v>
       </c>
-      <c r="Q60" s="6" t="inlineStr"/>
-      <c r="R60" s="6" t="inlineStr"/>
-      <c r="S60" s="6" t="inlineStr"/>
-      <c r="T60" s="6" t="inlineStr"/>
-      <c r="U60" s="6" t="inlineStr"/>
-      <c r="V60" s="6" t="inlineStr"/>
-      <c r="W60" s="6" t="inlineStr"/>
-      <c r="X60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5098,10 +4119,10 @@
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="5" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.01549209369771554</v>
+        <v>0.0168</v>
       </c>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
@@ -5114,14 +4135,6 @@
       <c r="P61" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="Q61" s="6" t="inlineStr"/>
-      <c r="R61" s="6" t="inlineStr"/>
-      <c r="S61" s="6" t="inlineStr"/>
-      <c r="T61" s="6" t="inlineStr"/>
-      <c r="U61" s="6" t="inlineStr"/>
-      <c r="V61" s="6" t="inlineStr"/>
-      <c r="W61" s="6" t="inlineStr"/>
-      <c r="X61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5160,10 +4173,10 @@
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="5" t="n">
-        <v>0.0152698174121777</v>
+        <v>0.0155</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.05647674886976661</v>
+        <v>0.055</v>
       </c>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
@@ -5176,14 +4189,6 @@
       <c r="P62" s="5" t="n">
         <v>0.9605</v>
       </c>
-      <c r="Q62" s="6" t="inlineStr"/>
-      <c r="R62" s="6" t="inlineStr"/>
-      <c r="S62" s="6" t="inlineStr"/>
-      <c r="T62" s="6" t="inlineStr"/>
-      <c r="U62" s="6" t="inlineStr"/>
-      <c r="V62" s="6" t="inlineStr"/>
-      <c r="W62" s="6" t="inlineStr"/>
-      <c r="X62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5222,10 +4227,10 @@
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="5" t="n">
-        <v>0.02413402691172006</v>
+        <v>0.0239</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0.01801957715632962</v>
+        <v>0.0178</v>
       </c>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
@@ -5238,14 +4243,6 @@
       <c r="P63" s="5" t="n">
         <v>0.9483</v>
       </c>
-      <c r="Q63" s="6" t="inlineStr"/>
-      <c r="R63" s="6" t="inlineStr"/>
-      <c r="S63" s="6" t="inlineStr"/>
-      <c r="T63" s="6" t="inlineStr"/>
-      <c r="U63" s="6" t="inlineStr"/>
-      <c r="V63" s="6" t="inlineStr"/>
-      <c r="W63" s="6" t="inlineStr"/>
-      <c r="X63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5283,11 +4280,9 @@
         <v>396</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="5" t="n">
-        <v>0.008069608842382725</v>
-      </c>
+      <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="n">
-        <v>0.01353835130051628</v>
+        <v>0.0134</v>
       </c>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
@@ -5300,14 +4295,6 @@
       <c r="P64" s="5" t="n">
         <v>0.9578</v>
       </c>
-      <c r="Q64" s="6" t="inlineStr"/>
-      <c r="R64" s="6" t="inlineStr"/>
-      <c r="S64" s="6" t="inlineStr"/>
-      <c r="T64" s="6" t="inlineStr"/>
-      <c r="U64" s="6" t="inlineStr"/>
-      <c r="V64" s="6" t="inlineStr"/>
-      <c r="W64" s="6" t="inlineStr"/>
-      <c r="X64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5346,10 +4333,10 @@
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="5" t="n">
-        <v>0.004799051310686364</v>
+        <v>0.0048</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>0.005648149462149199</v>
+        <v>0.0056</v>
       </c>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
@@ -5362,14 +4349,6 @@
       <c r="P65" s="5" t="n">
         <v>0.8683999999999999</v>
       </c>
-      <c r="Q65" s="6" t="inlineStr"/>
-      <c r="R65" s="6" t="inlineStr"/>
-      <c r="S65" s="6" t="inlineStr"/>
-      <c r="T65" s="6" t="inlineStr"/>
-      <c r="U65" s="6" t="inlineStr"/>
-      <c r="V65" s="6" t="inlineStr"/>
-      <c r="W65" s="6" t="inlineStr"/>
-      <c r="X65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5408,10 +4387,10 @@
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="5" t="n">
-        <v>0.03591177586380856</v>
+        <v>0.0354</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0.06550375398343611</v>
+        <v>0.064</v>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
@@ -5424,14 +4403,6 @@
       <c r="P66" s="5" t="n">
         <v>0.8871</v>
       </c>
-      <c r="Q66" s="6" t="inlineStr"/>
-      <c r="R66" s="6" t="inlineStr"/>
-      <c r="S66" s="6" t="inlineStr"/>
-      <c r="T66" s="6" t="inlineStr"/>
-      <c r="U66" s="6" t="inlineStr"/>
-      <c r="V66" s="6" t="inlineStr"/>
-      <c r="W66" s="6" t="inlineStr"/>
-      <c r="X66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5470,10 +4441,10 @@
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="5" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
@@ -5486,14 +4457,6 @@
       <c r="P67" s="5" t="n">
         <v>1.0006</v>
       </c>
-      <c r="Q67" s="6" t="inlineStr"/>
-      <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="inlineStr"/>
-      <c r="T67" s="6" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr"/>
-      <c r="V67" s="6" t="inlineStr"/>
-      <c r="W67" s="6" t="inlineStr"/>
-      <c r="X67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5532,10 +4495,10 @@
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="5" t="n">
-        <v>0.02932844669074952</v>
+        <v>0.0291</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>0.05790697714739124</v>
+        <v>0.0573</v>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
@@ -5548,14 +4511,6 @@
       <c r="P68" s="5" t="n">
         <v>0.8286</v>
       </c>
-      <c r="Q68" s="6" t="inlineStr"/>
-      <c r="R68" s="6" t="inlineStr"/>
-      <c r="S68" s="6" t="inlineStr"/>
-      <c r="T68" s="6" t="inlineStr"/>
-      <c r="U68" s="6" t="inlineStr"/>
-      <c r="V68" s="6" t="inlineStr"/>
-      <c r="W68" s="6" t="inlineStr"/>
-      <c r="X68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5594,10 +4549,10 @@
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="5" t="n">
-        <v>0.01613384681029095</v>
+        <v>0.0157</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>0.03042207487870752</v>
+        <v>0.0294</v>
       </c>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
@@ -5610,14 +4565,6 @@
       <c r="P69" s="5" t="n">
         <v>0.9645</v>
       </c>
-      <c r="Q69" s="6" t="inlineStr"/>
-      <c r="R69" s="6" t="inlineStr"/>
-      <c r="S69" s="6" t="inlineStr"/>
-      <c r="T69" s="6" t="inlineStr"/>
-      <c r="U69" s="6" t="inlineStr"/>
-      <c r="V69" s="6" t="inlineStr"/>
-      <c r="W69" s="6" t="inlineStr"/>
-      <c r="X69" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5630,7 +4577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5642,146 +4589,62 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3</t>
-        </is>
-      </c>
-      <c r="O1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="P1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_CURTAILMENT_AVG</t>
-        </is>
-      </c>
-      <c r="Q1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1</t>
-        </is>
-      </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY1_LABEL</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2</t>
-        </is>
-      </c>
-      <c r="T1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY2_LABEL</t>
-        </is>
-      </c>
-      <c r="U1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3</t>
-        </is>
-      </c>
-      <c r="V1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_FY3_LABEL</t>
-        </is>
-      </c>
-      <c r="W1" s="7" t="inlineStr">
-        <is>
-          <t>ISP_OFFLOADING_AVG</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>AVLSF1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5796,10 +4659,10 @@
         <v>0.8245</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.05408598823176547</v>
+        <v>0.0511</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1498933489306341</v>
+        <v>0.1441</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -5807,68 +4670,14 @@
       <c r="I2" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>BERYLSF1</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5883,10 +4692,10 @@
         <v>0.9235</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.05478264603755456</v>
+        <v>0.0521</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.1357018019333979</v>
+        <v>0.128</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0.636442356808484</v>
@@ -5894,68 +4703,14 @@
       <c r="I3" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="J3" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>BOMENSF1</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5970,10 +4725,10 @@
         <v>0.869</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.1440247773689721</v>
+        <v>0.132</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1299222960127742</v>
+        <v>0.123</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -5981,68 +4736,14 @@
       <c r="I4" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>BROKENH1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6057,10 +4758,10 @@
         <v>0.8405</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1211386533906305</v>
+        <v>0.115</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.156935340089925</v>
+        <v>0.1492</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0.399270575823056</v>
@@ -6068,68 +4769,14 @@
       <c r="I5" s="5" t="n">
         <v>0.017550018083952</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>0.06999999999999999</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>CESF1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6147,52 +4794,14 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>COLEASF1</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6207,10 +4816,10 @@
         <v>0.825</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03269498787171465</v>
+        <v>0.0327</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.02926126425553777</v>
+        <v>0.0292</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0.64186785726147</v>
@@ -6218,52 +4827,14 @@
       <c r="I7" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>CRWASF1</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6278,10 +4849,10 @@
         <v>0.8778</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.09614342553807431</v>
+        <v>0.0862</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.08192117087777062</v>
+        <v>0.0799</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0.529503172508041</v>
@@ -6289,68 +4860,14 @@
       <c r="I8" s="5" t="n">
         <v>7.253613938629221e-05</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CUSF1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6365,57 +4882,17 @@
         <v>0.8853</v>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>DARLSF1</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6430,10 +4907,10 @@
         <v>0.8395</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.06953767632819552</v>
+        <v>0.0636</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0882066342370772</v>
+        <v>0.0833</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0.64186785726147</v>
@@ -6441,52 +4918,14 @@
       <c r="I10" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FINLYSF1</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6501,10 +4940,10 @@
         <v>0.8387</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.07039079639714096</v>
+        <v>0.0643</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.08061793088892344</v>
+        <v>0.0762</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0.7032826997896851</v>
@@ -6512,52 +4951,14 @@
       <c r="I11" s="5" t="n">
         <v>0.264676213474225</v>
       </c>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>GESF1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6573,52 +4974,14 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr"/>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="inlineStr"/>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>GOONSF1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6633,10 +4996,10 @@
         <v>0.8827</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.138756180474872</v>
+        <v>0.132</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.3633793594193425</v>
+        <v>0.3285</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0.87127903942823</v>
@@ -6644,68 +5007,14 @@
       <c r="I13" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="J13" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>GRIFSF1</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6727,52 +5036,14 @@
       <c r="I14" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr"/>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr"/>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr"/>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>GULLRSF1</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6787,10 +5058,10 @@
         <v>0.9605</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.03485234997163289</v>
+        <v>0.0328</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1455688224294164</v>
+        <v>0.1353</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0.165388664850326</v>
@@ -6798,52 +5069,14 @@
       <c r="I15" s="5" t="n">
         <v>0.000681438300925263</v>
       </c>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr"/>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="inlineStr"/>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="inlineStr"/>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>GNNDHSF1</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6858,10 +5091,10 @@
         <v>0.8473000000000001</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1353701649733416</v>
+        <v>0.1268</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1888177292264882</v>
+        <v>0.1778</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0.903607825126104</v>
@@ -6869,68 +5102,14 @@
       <c r="I16" s="5" t="n">
         <v>0.900375357730696</v>
       </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.006666666666666667</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0.07666666666666667</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>HILLSTN1</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6945,10 +5124,10 @@
         <v>0.848</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1441759394227755</v>
+        <v>0.1304</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.3082526071352186</v>
+        <v>0.2781</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0.64186785726147</v>
@@ -6956,52 +5135,14 @@
       <c r="I17" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr"/>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="inlineStr"/>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="inlineStr"/>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>JEMALNG1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7016,10 +5157,10 @@
         <v>0.8823</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.07290536050268626</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1189868785607631</v>
+        <v>0.1147</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0.87127903942823</v>
@@ -7027,52 +5168,14 @@
       <c r="I18" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
-      <c r="R18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S18" s="5" t="inlineStr"/>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="inlineStr"/>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>JUNEESF1</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7087,10 +5190,10 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.1624878107170906</v>
+        <v>0.1534</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.2969960740318008</v>
+        <v>0.2801</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -7098,68 +5201,14 @@
       <c r="I19" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>LIMOSF11</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7174,10 +5223,10 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1329559142410704</v>
+        <v>0.1138</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2548659571637795</v>
+        <v>0.2431</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.505349468159863</v>
@@ -7185,68 +5234,14 @@
       <c r="I20" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>LIMOSF21</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7261,10 +5256,10 @@
         <v>0.8143</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.1373179274132644</v>
+        <v>0.1244</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.2539757919262627</v>
+        <v>0.2403</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.505349468159863</v>
@@ -7272,68 +5267,14 @@
       <c r="I21" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="J21" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>MANSLR1</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7348,10 +5289,10 @@
         <v>0.9397</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.5229812164970579</v>
+        <v>0.4514</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.6709166872938147</v>
+        <v>0.5511</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0.919931770355409</v>
@@ -7359,68 +5300,14 @@
       <c r="I22" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>METZSF1</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7435,10 +5322,10 @@
         <v>0.8702</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.007190464584342027</v>
+        <v>0.0075</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.07108174352041219</v>
+        <v>0.0614</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0.231026075027885</v>
@@ -7446,68 +5333,14 @@
       <c r="I23" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>MOLNGSF1</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7522,10 +5355,10 @@
         <v>0.9517</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.5764125048753213</v>
+        <v>0.488</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.6755707391955864</v>
+        <v>0.5639</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0.919931770355409</v>
@@ -7533,68 +5366,14 @@
       <c r="I24" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>MOREESF1</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7609,10 +5388,10 @@
         <v>0.8541</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.01188361985022102</v>
+        <v>0.012</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.001815619300523097</v>
+        <v>0.0089</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0.188257195450457</v>
@@ -7620,68 +5399,14 @@
       <c r="I25" s="5" t="n">
         <v>0.0686562187806459</v>
       </c>
-      <c r="J25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0.006666666666666667</v>
-      </c>
-      <c r="Q25" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="n">
-        <v>0.07666666666666667</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>MLSP1</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7699,52 +5424,14 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr"/>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr"/>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>NASF1</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7766,52 +5453,14 @@
       <c r="I27" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U27" s="5" t="inlineStr"/>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>NEVERSF1</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7826,10 +5475,10 @@
         <v>0.9258999999999999</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.03231345345515402</v>
+        <v>0.0332</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.07990508599190627</v>
+        <v>0.078</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0.15663609258386</v>
@@ -7837,68 +5486,14 @@
       <c r="I28" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>NEWENSF1</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -7913,10 +5508,10 @@
         <v>0.8943</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.09252848872869046</v>
+        <v>0.0851</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.139740603518281</v>
+        <v>0.125</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0.231026075027885</v>
@@ -7924,68 +5519,14 @@
       <c r="I29" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>NEWENSF2</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8000,10 +5541,10 @@
         <v>0.8943</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.09865070018729849</v>
+        <v>0.0885</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1267494122393782</v>
+        <v>0.1153</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>0.231026075027885</v>
@@ -8011,68 +5552,14 @@
       <c r="I30" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>NYNGAN1</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8087,10 +5574,10 @@
         <v>0.9698</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.02789950205429714</v>
+        <v>0.0277</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.03926636218841828</v>
+        <v>0.0388</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0.15663609258386</v>
@@ -8098,68 +5585,14 @@
       <c r="I31" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="J31" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q31" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S31" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>PARSF1</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8174,10 +5607,10 @@
         <v>0.8827</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.1275049435515178</v>
+        <v>0.123</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.3039969269602842</v>
+        <v>0.2694</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>0.87127903942823</v>
@@ -8185,52 +5618,14 @@
       <c r="I32" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr"/>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
-      <c r="R32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S32" s="5" t="inlineStr"/>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>QPSFB1</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8246,52 +5641,14 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>ROYALLA1</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8309,52 +5666,14 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>SUNRSF1</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8369,10 +5688,10 @@
         <v>0.8098</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.1153540312661219</v>
+        <v>0.1059</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.1173458509370597</v>
+        <v>0.1146</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0.505349468159863</v>
@@ -8380,68 +5699,14 @@
       <c r="I35" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
-      <c r="J35" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S35" s="5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U35" s="5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="n">
-        <v>0.14</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>SEBSF1</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8456,10 +5721,10 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1912183081095272</v>
+        <v>0.1766</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.2595859755929798</v>
+        <v>0.2365</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>0.1571570475144</v>
@@ -8467,68 +5732,14 @@
       <c r="I36" s="5" t="n">
         <v>0.0362161714591237</v>
       </c>
-      <c r="J36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>SKSF1</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8550,52 +5761,14 @@
       <c r="I37" s="5" t="n">
         <v>0.000643212863569608</v>
       </c>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr"/>
-      <c r="R37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S37" s="5" t="inlineStr"/>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr"/>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>STUBSF1</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8610,77 +5783,21 @@
         <v>0.9421</v>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="n">
-        <v>0.1421915117897189</v>
-      </c>
+      <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="J38" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q38" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S38" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>STUBSF2</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8695,77 +5812,21 @@
         <v>0.9421</v>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="n">
-        <v>0.1466186570287763</v>
-      </c>
+      <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
-      <c r="J39" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q39" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S39" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U39" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W39" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>SUNTPSF1</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8780,10 +5841,10 @@
         <v>0.9054</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.1345570232002854</v>
+        <v>0.1231</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1216265245384226</v>
+        <v>0.1167</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>0.15663609258386</v>
@@ -8791,68 +5852,14 @@
       <c r="I40" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="J40" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S40" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U40" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W40" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>WAGGNSF1</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8867,10 +5874,10 @@
         <v>0.8686</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.1713544037663096</v>
+        <v>0.1585</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.2654827427546417</v>
+        <v>0.2501</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -8878,68 +5885,14 @@
       <c r="I41" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S41" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="T41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W41" s="5" t="n">
-        <v>0.03333333333333333</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>WLWLSF1</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -8954,61 +5907,21 @@
         <v>0.8796</v>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="n">
-        <v>0.1015077616127097</v>
-      </c>
+      <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr"/>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
-      <c r="R42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="inlineStr"/>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr"/>
-      <c r="V42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>WLWLSF2</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9023,61 +5936,21 @@
         <v>0.8783</v>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="n">
-        <v>0.08481628251174367</v>
-      </c>
+      <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-      <c r="R43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="inlineStr"/>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr"/>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>WELNSF1</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9091,11 +5964,9 @@
       <c r="E44" s="5" t="n">
         <v>0.9364</v>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="n">
-        <v>0.06566494744533402</v>
+        <v>0.0616</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>0.15663609258386</v>
@@ -9103,68 +5974,14 @@
       <c r="I44" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S44" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W44" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>WELLSF1</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9179,10 +5996,10 @@
         <v>0.9258999999999999</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.03240949212773014</v>
+        <v>0.0315</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.03166342025536539</v>
+        <v>0.0306</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0.15663609258386</v>
@@ -9190,68 +6007,14 @@
       <c r="I45" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
-      <c r="J45" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v>0.1433333333333333</v>
-      </c>
-      <c r="Q45" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="n">
-        <v>0.2066666666666667</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>WSTWYSF1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9266,10 +6029,10 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1526525054987787</v>
+        <v>0.1433</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.1992808636220385</v>
+        <v>0.1883</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>0.64186785726147</v>
@@ -9277,52 +6040,14 @@
       <c r="I46" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>WRSF1</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9337,10 +6062,10 @@
         <v>0.8286</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.06560284749189083</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.06534439203754416</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0.231026075027885</v>
@@ -9348,68 +6073,14 @@
       <c r="I47" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
-      <c r="J47" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v>0.1633333333333333</v>
-      </c>
-      <c r="Q47" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="n">
-        <v>0.2533333333333334</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>WOLARSF1</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9424,61 +6095,21 @@
         <v>0.9548</v>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="n">
-        <v>0.2050867232572048</v>
-      </c>
+      <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="n">
         <v>0.158699742317549</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>0.000581408571101005</v>
       </c>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>WYASF1</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -9493,10 +6124,10 @@
         <v>0.8725000000000001</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.2305077708506661</v>
+        <v>0.2031</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.2071952920335971</v>
+        <v>0.1969</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>0.5859908275658871</v>
@@ -9504,52 +6135,14 @@
       <c r="I49" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>BANGOWF1</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9564,59 +6157,21 @@
         <v>0.9214</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.04243716720025748</v>
+        <v>0.042</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.05545881975491462</v>
+        <v>0.0528</v>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>BANGOWF2</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9631,59 +6186,21 @@
         <v>0.9349</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.1040645720677824</v>
+        <v>0.0983</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.1371023035528832</v>
+        <v>0.1308</v>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S51" s="5" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>BOCORWF1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9698,59 +6215,21 @@
         <v>0.958</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.006039051040345522</v>
+        <v>0.006</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.01443946864179979</v>
+        <v>0.0143</v>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>BODWF1</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9765,59 +6244,21 @@
         <v>0.9544</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.02140267904180271</v>
+        <v>0.0213</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.02661806541842593</v>
+        <v>0.0265</v>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="inlineStr"/>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>CAPTL_WF</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9835,52 +6276,14 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>COLWF01</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9895,59 +6298,21 @@
         <v>0.9608</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.004724844204588741</v>
+        <v>0.0066</v>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-      <c r="R55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S55" s="5" t="inlineStr"/>
-      <c r="T55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>CROOKWF2</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -9961,60 +6326,18 @@
       <c r="E56" s="5" t="n">
         <v>0.9619</v>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>0.005091820276778458</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.0348272517253635</v>
-      </c>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr"/>
-      <c r="R56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S56" s="5" t="inlineStr"/>
-      <c r="T56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U56" s="5" t="inlineStr"/>
-      <c r="V56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>CROOKWF3</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10028,60 +6351,18 @@
       <c r="E57" s="5" t="n">
         <v>0.9615</v>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.04302205984473428</v>
-      </c>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr"/>
-      <c r="R57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S57" s="5" t="inlineStr"/>
-      <c r="T57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U57" s="5" t="inlineStr"/>
-      <c r="V57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>CRURWF1</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10096,59 +6377,21 @@
         <v>0.9276</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.01096445117417066</v>
+        <v>0.0109</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.03115483200409874</v>
+        <v>0.0298</v>
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr"/>
-      <c r="R58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S58" s="5" t="inlineStr"/>
-      <c r="T58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U58" s="5" t="inlineStr"/>
-      <c r="V58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>CULLRGWF</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10166,52 +6409,14 @@
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr"/>
-      <c r="R59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S59" s="5" t="inlineStr"/>
-      <c r="T59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>FLYCRKWF</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10225,60 +6430,20 @@
       <c r="E60" s="5" t="n">
         <v>1.0041</v>
       </c>
-      <c r="F60" s="5" t="n">
-        <v>0.02821751962877717</v>
-      </c>
+      <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="n">
-        <v>0.05196807492452316</v>
+        <v>0.0509</v>
       </c>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr"/>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr"/>
-      <c r="R60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S60" s="5" t="inlineStr"/>
-      <c r="T60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U60" s="5" t="inlineStr"/>
-      <c r="V60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>GULLRWF1</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10293,59 +6458,21 @@
         <v>0.9605</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.01549209369771554</v>
+        <v>0.0168</v>
       </c>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N61" s="5" t="inlineStr"/>
-      <c r="O61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr"/>
-      <c r="R61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S61" s="5" t="inlineStr"/>
-      <c r="T61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U61" s="5" t="inlineStr"/>
-      <c r="V61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>GULLRWF2</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10360,59 +6487,21 @@
         <v>0.9605</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.0152698174121777</v>
+        <v>0.0155</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.05647674886976661</v>
+        <v>0.055</v>
       </c>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="inlineStr"/>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr"/>
-      <c r="R62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S62" s="5" t="inlineStr"/>
-      <c r="T62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U62" s="5" t="inlineStr"/>
-      <c r="V62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>GUNNING1</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10427,59 +6516,21 @@
         <v>0.9483</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.02413402691172006</v>
+        <v>0.0239</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.01801957715632962</v>
+        <v>0.0178</v>
       </c>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N63" s="5" t="inlineStr"/>
-      <c r="O63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr"/>
-      <c r="R63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S63" s="5" t="inlineStr"/>
-      <c r="T63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U63" s="5" t="inlineStr"/>
-      <c r="V63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>RYEPARK1</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10493,60 +6544,20 @@
       <c r="E64" s="5" t="n">
         <v>0.9578</v>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>0.008069608842382725</v>
-      </c>
+      <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="n">
-        <v>0.01353835130051628</v>
+        <v>0.0134</v>
       </c>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L64" s="5" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N64" s="5" t="inlineStr"/>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr"/>
-      <c r="R64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S64" s="5" t="inlineStr"/>
-      <c r="T64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U64" s="5" t="inlineStr"/>
-      <c r="V64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>SAPHWF1</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10561,59 +6572,21 @@
         <v>0.8683999999999999</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.004799051310686364</v>
+        <v>0.0048</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.005648149462149199</v>
+        <v>0.0056</v>
       </c>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr"/>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr"/>
-      <c r="O65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="5" t="inlineStr"/>
-      <c r="R65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S65" s="5" t="inlineStr"/>
-      <c r="T65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U65" s="5" t="inlineStr"/>
-      <c r="V65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>STWF1</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10628,59 +6601,21 @@
         <v>0.8871</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.03591177586380856</v>
+        <v>0.0354</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.06550375398343611</v>
+        <v>0.064</v>
       </c>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="inlineStr"/>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr"/>
-      <c r="R66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S66" s="5" t="inlineStr"/>
-      <c r="T66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U66" s="5" t="inlineStr"/>
-      <c r="V66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>TARALGA1</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10695,59 +6630,21 @@
         <v>1.0006</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr"/>
-      <c r="R67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S67" s="5" t="inlineStr"/>
-      <c r="T67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U67" s="5" t="inlineStr"/>
-      <c r="V67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>WRWF1</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10762,59 +6659,21 @@
         <v>0.8286</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.02932844669074952</v>
+        <v>0.0291</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.05790697714739124</v>
+        <v>0.0573</v>
       </c>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr"/>
-      <c r="M68" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N68" s="5" t="inlineStr"/>
-      <c r="O68" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P68" s="5" t="inlineStr"/>
-      <c r="Q68" s="5" t="inlineStr"/>
-      <c r="R68" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S68" s="5" t="inlineStr"/>
-      <c r="T68" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U68" s="5" t="inlineStr"/>
-      <c r="V68" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>WOODLWN1</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -10829,51 +6688,13 @@
         <v>0.9645</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.01613384681029095</v>
+        <v>0.0157</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.03042207487870752</v>
+        <v>0.0294</v>
       </c>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="inlineStr"/>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="N69" s="5" t="inlineStr"/>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="P69" s="5" t="inlineStr"/>
-      <c r="Q69" s="5" t="inlineStr"/>
-      <c r="R69" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="S69" s="5" t="inlineStr"/>
-      <c r="T69" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="U69" s="5" t="inlineStr"/>
-      <c r="V69" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="W69" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C69">
@@ -10960,174 +6781,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J69">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K69">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L69">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M69">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N69">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O69">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P69">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q69">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R69">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S69">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T69">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U69">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V69">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W69">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="0063BE7B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="00F8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +475,14 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,6 +566,46 @@
           <t>FY26-27 (Draft)</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -619,6 +670,30 @@
       <c r="P2" s="5" t="n">
         <v>0.8245</v>
       </c>
+      <c r="Q2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X2" s="6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -683,6 +758,30 @@
       <c r="P3" s="5" t="n">
         <v>0.9235</v>
       </c>
+      <c r="Q3" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W3" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X3" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -747,6 +846,30 @@
       <c r="P4" s="5" t="n">
         <v>0.869</v>
       </c>
+      <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X4" s="6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -810,6 +933,30 @@
       </c>
       <c r="P5" s="5" t="n">
         <v>0.8405</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>0.06999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -861,6 +1008,14 @@
       <c r="P6" s="5" t="n">
         <v>0.9961</v>
       </c>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr"/>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
+      <c r="X6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -925,6 +1080,14 @@
       <c r="P7" s="5" t="n">
         <v>0.825</v>
       </c>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr"/>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
+      <c r="X7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -988,6 +1151,30 @@
       </c>
       <c r="P8" s="5" t="n">
         <v>0.8778</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W8" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X8" s="6" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="9">
@@ -1039,6 +1226,14 @@
       <c r="P9" s="5" t="n">
         <v>0.8853</v>
       </c>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1103,6 +1298,14 @@
       <c r="P10" s="5" t="n">
         <v>0.8395</v>
       </c>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr"/>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
+      <c r="X10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1167,6 +1370,14 @@
       <c r="P11" s="5" t="n">
         <v>0.8387</v>
       </c>
+      <c r="Q11" s="6" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="6" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="6" t="inlineStr"/>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
+      <c r="X11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1215,6 +1426,14 @@
       <c r="P12" s="5" t="n">
         <v>0.884</v>
       </c>
+      <c r="Q12" s="6" t="inlineStr"/>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="6" t="inlineStr"/>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="6" t="inlineStr"/>
+      <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="6" t="inlineStr"/>
+      <c r="X12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1278,6 +1497,30 @@
       </c>
       <c r="P13" s="5" t="n">
         <v>0.8827</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X13" s="6" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1339,6 +1582,14 @@
       <c r="P14" s="5" t="n">
         <v>0.8493000000000001</v>
       </c>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="6" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="6" t="inlineStr"/>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
+      <c r="X14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1403,6 +1654,14 @@
       <c r="P15" s="5" t="n">
         <v>0.9605</v>
       </c>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="6" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="6" t="inlineStr"/>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="6" t="inlineStr"/>
+      <c r="X15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1467,6 +1726,30 @@
       <c r="P16" s="5" t="n">
         <v>0.8473000000000001</v>
       </c>
+      <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X16" s="6" t="n">
+        <v>0.07666666666666667</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1531,6 +1814,14 @@
       <c r="P17" s="5" t="n">
         <v>0.848</v>
       </c>
+      <c r="Q17" s="6" t="inlineStr"/>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="6" t="inlineStr"/>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="6" t="inlineStr"/>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="6" t="inlineStr"/>
+      <c r="X17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1595,6 +1886,14 @@
       <c r="P18" s="5" t="n">
         <v>0.8823</v>
       </c>
+      <c r="Q18" s="6" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="6" t="inlineStr"/>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
+      <c r="X18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1659,6 +1958,30 @@
       <c r="P19" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X19" s="6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1723,6 +2046,30 @@
       <c r="P20" s="5" t="n">
         <v>0.8090000000000001</v>
       </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X20" s="6" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1787,6 +2134,30 @@
       <c r="P21" s="5" t="n">
         <v>0.8143</v>
       </c>
+      <c r="Q21" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X21" s="6" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1851,6 +2222,30 @@
       <c r="P22" s="5" t="n">
         <v>0.9397</v>
       </c>
+      <c r="Q22" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W22" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X22" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1915,6 +2310,30 @@
       <c r="P23" s="5" t="n">
         <v>0.8702</v>
       </c>
+      <c r="Q23" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X23" s="6" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1979,6 +2398,30 @@
       <c r="P24" s="5" t="n">
         <v>0.9517</v>
       </c>
+      <c r="Q24" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X24" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2042,6 +2485,30 @@
       </c>
       <c r="P25" s="5" t="n">
         <v>0.8541</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W25" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X25" s="6" t="n">
+        <v>0.07666666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -2093,6 +2560,14 @@
       <c r="P26" s="5" t="n">
         <v>0.9799</v>
       </c>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr"/>
+      <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2153,6 +2628,14 @@
       <c r="P27" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2217,6 +2700,30 @@
       <c r="P28" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
+      <c r="Q28" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S28" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V28" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W28" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X28" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2281,6 +2788,30 @@
       <c r="P29" s="5" t="n">
         <v>0.8943</v>
       </c>
+      <c r="Q29" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="U29" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X29" s="6" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2345,6 +2876,30 @@
       <c r="P30" s="5" t="n">
         <v>0.8943</v>
       </c>
+      <c r="Q30" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="U30" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X30" s="6" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2409,6 +2964,30 @@
       <c r="P31" s="5" t="n">
         <v>0.9698</v>
       </c>
+      <c r="Q31" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X31" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2473,6 +3052,14 @@
       <c r="P32" s="5" t="n">
         <v>0.8827</v>
       </c>
+      <c r="Q32" s="6" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr"/>
+      <c r="V32" s="6" t="inlineStr"/>
+      <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2521,6 +3108,14 @@
       <c r="P33" s="5" t="n">
         <v>0.8863</v>
       </c>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2571,6 +3166,14 @@
       <c r="P34" s="5" t="n">
         <v>0.9656</v>
       </c>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr"/>
+      <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2635,6 +3238,30 @@
       <c r="P35" s="5" t="n">
         <v>0.8098</v>
       </c>
+      <c r="Q35" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X35" s="6" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2698,6 +3325,30 @@
       </c>
       <c r="P36" s="5" t="n">
         <v>0.8725000000000001</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X36" s="6" t="n">
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -2759,6 +3410,14 @@
       <c r="P37" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
+      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr"/>
+      <c r="V37" s="6" t="inlineStr"/>
+      <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2819,6 +3478,30 @@
       <c r="P38" s="5" t="n">
         <v>0.9421</v>
       </c>
+      <c r="Q38" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S38" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T38" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U38" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V38" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W38" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X38" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2879,6 +3562,30 @@
       <c r="P39" s="5" t="n">
         <v>0.9421</v>
       </c>
+      <c r="Q39" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X39" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2943,6 +3650,30 @@
       <c r="P40" s="5" t="n">
         <v>0.9054</v>
       </c>
+      <c r="Q40" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X40" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3006,6 +3737,30 @@
       </c>
       <c r="P41" s="5" t="n">
         <v>0.8686</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X41" s="6" t="n">
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="42">
@@ -3067,6 +3822,14 @@
       <c r="P42" s="5" t="n">
         <v>0.8796</v>
       </c>
+      <c r="Q42" s="6" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr"/>
+      <c r="V42" s="6" t="inlineStr"/>
+      <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3127,6 +3890,14 @@
       <c r="P43" s="5" t="n">
         <v>0.8783</v>
       </c>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3189,6 +3960,30 @@
       <c r="P44" s="5" t="n">
         <v>0.9364</v>
       </c>
+      <c r="Q44" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W44" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X44" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3253,6 +4048,30 @@
       <c r="P45" s="5" t="n">
         <v>0.9258999999999999</v>
       </c>
+      <c r="Q45" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="U45" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="W45" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X45" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3317,6 +4136,14 @@
       <c r="P46" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
+      <c r="Q46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr"/>
+      <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3380,6 +4207,30 @@
       </c>
       <c r="P47" s="5" t="n">
         <v>0.8286</v>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T47" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="U47" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V47" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W47" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X47" s="6" t="n">
+        <v>0.2533333333333334</v>
       </c>
     </row>
     <row r="48">
@@ -3441,6 +4292,14 @@
       <c r="P48" s="5" t="n">
         <v>0.9548</v>
       </c>
+      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr"/>
+      <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3505,6 +4364,14 @@
       <c r="P49" s="5" t="n">
         <v>0.8725000000000001</v>
       </c>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3559,6 +4426,14 @@
       <c r="P50" s="5" t="n">
         <v>0.9214</v>
       </c>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3613,6 +4488,14 @@
       <c r="P51" s="5" t="n">
         <v>0.9349</v>
       </c>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3667,6 +4550,14 @@
       <c r="P52" s="5" t="n">
         <v>0.958</v>
       </c>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3721,6 +4612,14 @@
       <c r="P53" s="5" t="n">
         <v>0.9544</v>
       </c>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3771,6 +4670,14 @@
       <c r="P54" s="5" t="n">
         <v>0.9645</v>
       </c>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3825,6 +4732,14 @@
       <c r="P55" s="5" t="n">
         <v>0.9608</v>
       </c>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3875,6 +4790,14 @@
       <c r="P56" s="5" t="n">
         <v>0.9619</v>
       </c>
+      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr"/>
+      <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3925,6 +4848,14 @@
       <c r="P57" s="5" t="n">
         <v>0.9615</v>
       </c>
+      <c r="Q57" s="6" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr"/>
+      <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3979,6 +4910,14 @@
       <c r="P58" s="5" t="n">
         <v>0.9276</v>
       </c>
+      <c r="Q58" s="6" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr"/>
+      <c r="T58" s="6" t="inlineStr"/>
+      <c r="U58" s="6" t="inlineStr"/>
+      <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
+      <c r="X58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4029,6 +4968,14 @@
       <c r="P59" s="5" t="n">
         <v>0.9483</v>
       </c>
+      <c r="Q59" s="6" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr"/>
+      <c r="T59" s="6" t="inlineStr"/>
+      <c r="U59" s="6" t="inlineStr"/>
+      <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
+      <c r="X59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4081,6 +5028,14 @@
       <c r="P60" s="5" t="n">
         <v>1.0041</v>
       </c>
+      <c r="Q60" s="6" t="inlineStr"/>
+      <c r="R60" s="6" t="inlineStr"/>
+      <c r="S60" s="6" t="inlineStr"/>
+      <c r="T60" s="6" t="inlineStr"/>
+      <c r="U60" s="6" t="inlineStr"/>
+      <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
+      <c r="X60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4135,6 +5090,14 @@
       <c r="P61" s="5" t="n">
         <v>0.9605</v>
       </c>
+      <c r="Q61" s="6" t="inlineStr"/>
+      <c r="R61" s="6" t="inlineStr"/>
+      <c r="S61" s="6" t="inlineStr"/>
+      <c r="T61" s="6" t="inlineStr"/>
+      <c r="U61" s="6" t="inlineStr"/>
+      <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4189,6 +5152,14 @@
       <c r="P62" s="5" t="n">
         <v>0.9605</v>
       </c>
+      <c r="Q62" s="6" t="inlineStr"/>
+      <c r="R62" s="6" t="inlineStr"/>
+      <c r="S62" s="6" t="inlineStr"/>
+      <c r="T62" s="6" t="inlineStr"/>
+      <c r="U62" s="6" t="inlineStr"/>
+      <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
+      <c r="X62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4243,6 +5214,14 @@
       <c r="P63" s="5" t="n">
         <v>0.9483</v>
       </c>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr"/>
+      <c r="S63" s="6" t="inlineStr"/>
+      <c r="T63" s="6" t="inlineStr"/>
+      <c r="U63" s="6" t="inlineStr"/>
+      <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
+      <c r="X63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4295,6 +5274,14 @@
       <c r="P64" s="5" t="n">
         <v>0.9578</v>
       </c>
+      <c r="Q64" s="6" t="inlineStr"/>
+      <c r="R64" s="6" t="inlineStr"/>
+      <c r="S64" s="6" t="inlineStr"/>
+      <c r="T64" s="6" t="inlineStr"/>
+      <c r="U64" s="6" t="inlineStr"/>
+      <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
+      <c r="X64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4349,6 +5336,14 @@
       <c r="P65" s="5" t="n">
         <v>0.8683999999999999</v>
       </c>
+      <c r="Q65" s="6" t="inlineStr"/>
+      <c r="R65" s="6" t="inlineStr"/>
+      <c r="S65" s="6" t="inlineStr"/>
+      <c r="T65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr"/>
+      <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
+      <c r="X65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4403,6 +5398,14 @@
       <c r="P66" s="5" t="n">
         <v>0.8871</v>
       </c>
+      <c r="Q66" s="6" t="inlineStr"/>
+      <c r="R66" s="6" t="inlineStr"/>
+      <c r="S66" s="6" t="inlineStr"/>
+      <c r="T66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr"/>
+      <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
+      <c r="X66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4457,6 +5460,14 @@
       <c r="P67" s="5" t="n">
         <v>1.0006</v>
       </c>
+      <c r="Q67" s="6" t="inlineStr"/>
+      <c r="R67" s="6" t="inlineStr"/>
+      <c r="S67" s="6" t="inlineStr"/>
+      <c r="T67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr"/>
+      <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
+      <c r="X67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4511,6 +5522,14 @@
       <c r="P68" s="5" t="n">
         <v>0.8286</v>
       </c>
+      <c r="Q68" s="6" t="inlineStr"/>
+      <c r="R68" s="6" t="inlineStr"/>
+      <c r="S68" s="6" t="inlineStr"/>
+      <c r="T68" s="6" t="inlineStr"/>
+      <c r="U68" s="6" t="inlineStr"/>
+      <c r="V68" s="6" t="inlineStr"/>
+      <c r="W68" s="6" t="inlineStr"/>
+      <c r="X68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4565,6 +5584,14 @@
       <c r="P69" s="5" t="n">
         <v>0.9645</v>
       </c>
+      <c r="Q69" s="6" t="inlineStr"/>
+      <c r="R69" s="6" t="inlineStr"/>
+      <c r="S69" s="6" t="inlineStr"/>
+      <c r="T69" s="6" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr"/>
+      <c r="V69" s="6" t="inlineStr"/>
+      <c r="W69" s="6" t="inlineStr"/>
+      <c r="X69" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4577,7 +5604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4589,62 +5616,146 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY24-25</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27 (Draft)</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AVLSF1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4670,14 +5781,68 @@
       <c r="I2" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>BERYLSF1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4703,14 +5868,68 @@
       <c r="I3" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
+      <c r="J3" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>BOMENSF1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4736,14 +5955,68 @@
       <c r="I4" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BROKENH1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4769,14 +6042,68 @@
       <c r="I5" s="5" t="n">
         <v>0.017550018083952</v>
       </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0.06999999999999999</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>CESF1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4794,14 +6121,52 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>COLEASF1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4827,14 +6192,52 @@
       <c r="I7" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CRWASF1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4860,14 +6263,68 @@
       <c r="I8" s="5" t="n">
         <v>7.253613938629221e-05</v>
       </c>
+      <c r="J8" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CUSF1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4885,14 +6342,52 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>DARLSF1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4918,14 +6413,52 @@
       <c r="I10" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>FINLYSF1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4951,14 +6484,52 @@
       <c r="I11" s="5" t="n">
         <v>0.264676213474225</v>
       </c>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>GESF1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4974,14 +6545,52 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>GOONSF1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5007,14 +6616,68 @@
       <c r="I13" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
+      <c r="J13" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>GRIFSF1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5036,14 +6699,52 @@
       <c r="I14" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>GULLRSF1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5069,14 +6770,52 @@
       <c r="I15" s="5" t="n">
         <v>0.000681438300925263</v>
       </c>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>GNNDHSF1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5102,14 +6841,68 @@
       <c r="I16" s="5" t="n">
         <v>0.900375357730696</v>
       </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>0.07666666666666667</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>HILLSTN1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5135,14 +6928,52 @@
       <c r="I17" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>JEMALNG1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5168,14 +6999,52 @@
       <c r="I18" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr"/>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>JUNEESF1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5201,14 +7070,68 @@
       <c r="I19" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>LIMOSF11</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5234,14 +7157,68 @@
       <c r="I20" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
+      <c r="J20" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>LIMOSF21</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5267,14 +7244,68 @@
       <c r="I21" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
+      <c r="J21" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>MANSLR1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5300,14 +7331,68 @@
       <c r="I22" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
+      <c r="J22" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>METZSF1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5333,14 +7418,68 @@
       <c r="I23" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="J23" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>MOLNGSF1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5366,14 +7505,68 @@
       <c r="I24" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
+      <c r="J24" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>MOREESF1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5399,14 +7592,68 @@
       <c r="I25" s="5" t="n">
         <v>0.0686562187806459</v>
       </c>
+      <c r="J25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="n">
+        <v>0.07666666666666667</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>MLSP1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5424,14 +7671,52 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>NASF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5453,14 +7738,52 @@
       <c r="I27" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr"/>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>NEVERSF1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5486,14 +7809,68 @@
       <c r="I28" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="J28" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>NEWENSF1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5519,14 +7896,68 @@
       <c r="I29" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="J29" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>NEWENSF2</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5552,14 +7983,68 @@
       <c r="I30" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="J30" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>NYNGAN1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5585,14 +8070,68 @@
       <c r="I31" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="J31" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>PARSF1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5618,14 +8157,52 @@
       <c r="I32" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>QPSFB1</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5641,14 +8218,52 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="inlineStr"/>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr"/>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>ROYALLA1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5666,14 +8281,52 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr"/>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>SUNRSF1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5699,14 +8352,68 @@
       <c r="I35" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
+      <c r="J35" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>SEBSF1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5732,14 +8439,68 @@
       <c r="I36" s="5" t="n">
         <v>0.0362161714591237</v>
       </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>SKSF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5761,14 +8522,52 @@
       <c r="I37" s="5" t="n">
         <v>0.000643212863569608</v>
       </c>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr"/>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>STUBSF1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5790,14 +8589,68 @@
       <c r="I38" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
+      <c r="J38" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>STUBSF2</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5819,14 +8672,68 @@
       <c r="I39" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
+      <c r="J39" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>SUNTPSF1</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5852,14 +8759,68 @@
       <c r="I40" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="J40" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>WAGGNSF1</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5885,14 +8846,68 @@
       <c r="I41" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>WLWLSF1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5914,14 +8929,52 @@
       <c r="I42" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>WLWLSF2</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5943,14 +8996,52 @@
       <c r="I43" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>WELNSF1</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5974,14 +9065,68 @@
       <c r="I44" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="J44" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>WELLSF1</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6007,14 +9152,68 @@
       <c r="I45" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="J45" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>WSTWYSF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6040,14 +9239,52 @@
       <c r="I46" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>WRSF1</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6073,14 +9310,68 @@
       <c r="I47" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="J47" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="Q47" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>WOLARSF1</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6102,14 +9393,52 @@
       <c r="I48" s="5" t="n">
         <v>0.000581408571101005</v>
       </c>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S48" s="5" t="inlineStr"/>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr"/>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>WYASF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -6135,14 +9464,52 @@
       <c r="I49" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr"/>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr"/>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>BANGOWF1</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6164,14 +9531,52 @@
       </c>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr"/>
+      <c r="T50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>BANGOWF2</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6193,14 +9598,52 @@
       </c>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S51" s="5" t="inlineStr"/>
+      <c r="T51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>BOCORWF1</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6222,14 +9665,52 @@
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr"/>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S52" s="5" t="inlineStr"/>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr"/>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>BODWF1</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6251,14 +9732,52 @@
       </c>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr"/>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr"/>
+      <c r="V53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>CAPTL_WF</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6276,14 +9795,52 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr"/>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S54" s="5" t="inlineStr"/>
+      <c r="T54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr"/>
+      <c r="V54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>COLWF01</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6305,14 +9862,52 @@
       </c>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="inlineStr"/>
+      <c r="T55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>CROOKWF2</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6330,14 +9925,52 @@
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr"/>
+      <c r="R56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="inlineStr"/>
+      <c r="T56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U56" s="5" t="inlineStr"/>
+      <c r="V56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>CROOKWF3</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6355,14 +9988,52 @@
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S57" s="5" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U57" s="5" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>CRURWF1</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6384,14 +10055,52 @@
       </c>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr"/>
+      <c r="R58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S58" s="5" t="inlineStr"/>
+      <c r="T58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr"/>
+      <c r="V58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>CULLRGWF</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6409,14 +10118,52 @@
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="R59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S59" s="5" t="inlineStr"/>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>FLYCRKWF</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6436,14 +10183,52 @@
       </c>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr"/>
+      <c r="R60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S60" s="5" t="inlineStr"/>
+      <c r="T60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U60" s="5" t="inlineStr"/>
+      <c r="V60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>GULLRWF1</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6465,14 +10250,52 @@
       </c>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S61" s="5" t="inlineStr"/>
+      <c r="T61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U61" s="5" t="inlineStr"/>
+      <c r="V61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>GULLRWF2</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6494,14 +10317,52 @@
       </c>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="R62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S62" s="5" t="inlineStr"/>
+      <c r="T62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U62" s="5" t="inlineStr"/>
+      <c r="V62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>GUNNING1</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6523,14 +10384,52 @@
       </c>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S63" s="5" t="inlineStr"/>
+      <c r="T63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U63" s="5" t="inlineStr"/>
+      <c r="V63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>RYEPARK1</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6550,14 +10449,52 @@
       </c>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr"/>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S64" s="5" t="inlineStr"/>
+      <c r="T64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U64" s="5" t="inlineStr"/>
+      <c r="V64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>SAPHWF1</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6579,14 +10516,52 @@
       </c>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr"/>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S65" s="5" t="inlineStr"/>
+      <c r="T65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U65" s="5" t="inlineStr"/>
+      <c r="V65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>STWF1</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6608,14 +10583,52 @@
       </c>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr"/>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S66" s="5" t="inlineStr"/>
+      <c r="T66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U66" s="5" t="inlineStr"/>
+      <c r="V66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>TARALGA1</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6637,14 +10650,52 @@
       </c>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S67" s="5" t="inlineStr"/>
+      <c r="T67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr"/>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>WRWF1</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6666,14 +10717,52 @@
       </c>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="inlineStr"/>
+      <c r="Q68" s="5" t="inlineStr"/>
+      <c r="R68" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S68" s="5" t="inlineStr"/>
+      <c r="T68" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="inlineStr"/>
+      <c r="V68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>WOODLWN1</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6695,6 +10784,44 @@
       </c>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="inlineStr"/>
+      <c r="Q69" s="5" t="inlineStr"/>
+      <c r="R69" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="S69" s="5" t="inlineStr"/>
+      <c r="T69" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="U69" s="5" t="inlineStr"/>
+      <c r="V69" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="W69" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C69">
@@ -6781,6 +10908,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J69">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K69">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L69">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M69">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N69">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q69">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R69">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S69">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T69">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U69">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V69">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W69">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -82,6 +82,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -453,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +474,14 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,6 +560,46 @@
           <t>FY26-27</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Curt FY3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curt Avg</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Offl FY3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Offl Avg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -610,6 +661,30 @@
       <c r="O2" s="5" t="n">
         <v>0.8395</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -671,6 +746,30 @@
       <c r="O3" s="5" t="n">
         <v>0.9245</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W3" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -732,6 +831,30 @@
       <c r="O4" s="5" t="n">
         <v>0.8823</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -792,6 +915,30 @@
       </c>
       <c r="O5" s="5" t="n">
         <v>0.8436</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0.06999999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -840,6 +987,14 @@
       <c r="O6" s="5" t="n">
         <v>1.0026</v>
       </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr"/>
+      <c r="V6" s="6" t="inlineStr"/>
+      <c r="W6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -901,6 +1056,14 @@
       <c r="O7" s="5" t="n">
         <v>0.8416</v>
       </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="6" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr"/>
+      <c r="V7" s="6" t="inlineStr"/>
+      <c r="W7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -961,6 +1124,30 @@
       </c>
       <c r="O8" s="5" t="n">
         <v>0.8899</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W8" s="6" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="9">
@@ -1009,6 +1196,14 @@
       <c r="O9" s="5" t="n">
         <v>0.8903</v>
       </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="6" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
+      <c r="W9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1070,6 +1265,14 @@
       <c r="O10" s="5" t="n">
         <v>0.8554</v>
       </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="6" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="6" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr"/>
+      <c r="V10" s="6" t="inlineStr"/>
+      <c r="W10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1131,6 +1334,14 @@
       <c r="O11" s="5" t="n">
         <v>0.8521</v>
       </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="6" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="6" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr"/>
+      <c r="U11" s="6" t="inlineStr"/>
+      <c r="V11" s="6" t="inlineStr"/>
+      <c r="W11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1178,6 +1389,14 @@
       <c r="O12" s="5" t="n">
         <v>0.8977000000000001</v>
       </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="6" t="inlineStr"/>
+      <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="6" t="inlineStr"/>
+      <c r="T12" s="6" t="inlineStr"/>
+      <c r="U12" s="6" t="inlineStr"/>
+      <c r="V12" s="6" t="inlineStr"/>
+      <c r="W12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1238,6 +1457,30 @@
       </c>
       <c r="O13" s="5" t="n">
         <v>0.8918</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V13" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W13" s="6" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1296,6 +1539,14 @@
       <c r="O14" s="5" t="n">
         <v>0.8653999999999999</v>
       </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="6" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr"/>
+      <c r="U14" s="6" t="inlineStr"/>
+      <c r="V14" s="6" t="inlineStr"/>
+      <c r="W14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1357,6 +1608,14 @@
       <c r="O15" s="5" t="n">
         <v>0.9635</v>
       </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="6" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr"/>
+      <c r="U15" s="6" t="inlineStr"/>
+      <c r="V15" s="6" t="inlineStr"/>
+      <c r="W15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1418,6 +1677,30 @@
       <c r="O16" s="5" t="n">
         <v>0.8463000000000001</v>
       </c>
+      <c r="P16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U16" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V16" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W16" s="6" t="n">
+        <v>0.07666666666666667</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1479,6 +1762,14 @@
       <c r="O17" s="5" t="n">
         <v>0.8652</v>
       </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr"/>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="6" t="inlineStr"/>
+      <c r="T17" s="6" t="inlineStr"/>
+      <c r="U17" s="6" t="inlineStr"/>
+      <c r="V17" s="6" t="inlineStr"/>
+      <c r="W17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1540,6 +1831,14 @@
       <c r="O18" s="5" t="n">
         <v>0.8962</v>
       </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="6" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="6" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr"/>
+      <c r="U18" s="6" t="inlineStr"/>
+      <c r="V18" s="6" t="inlineStr"/>
+      <c r="W18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1601,6 +1900,30 @@
       <c r="O19" s="5" t="n">
         <v>0.8865</v>
       </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1662,6 +1985,30 @@
       <c r="O20" s="5" t="n">
         <v>0.8206</v>
       </c>
+      <c r="P20" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1723,6 +2070,30 @@
       <c r="O21" s="5" t="n">
         <v>0.8268</v>
       </c>
+      <c r="P21" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1784,6 +2155,30 @@
       <c r="O22" s="5" t="n">
         <v>0.9482</v>
       </c>
+      <c r="P22" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U22" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V22" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W22" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1845,6 +2240,30 @@
       <c r="O23" s="5" t="n">
         <v>0.8657</v>
       </c>
+      <c r="P23" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1906,6 +2325,30 @@
       <c r="O24" s="5" t="n">
         <v>0.9583</v>
       </c>
+      <c r="P24" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1966,6 +2409,30 @@
       </c>
       <c r="O25" s="5" t="n">
         <v>0.8509</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W25" s="6" t="n">
+        <v>0.07666666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -2014,6 +2481,14 @@
       <c r="O26" s="5" t="n">
         <v>0.9708</v>
       </c>
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr"/>
+      <c r="S26" s="6" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr"/>
+      <c r="V26" s="6" t="inlineStr"/>
+      <c r="W26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2057,6 +2532,14 @@
       <c r="M27" s="5" t="inlineStr"/>
       <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr"/>
+      <c r="V27" s="6" t="inlineStr"/>
+      <c r="W27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2114,6 +2597,14 @@
       <c r="O28" s="5" t="n">
         <v>0.9273</v>
       </c>
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr"/>
+      <c r="U28" s="6" t="inlineStr"/>
+      <c r="V28" s="6" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2175,6 +2666,30 @@
       <c r="O29" s="5" t="n">
         <v>0.9273</v>
       </c>
+      <c r="P29" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U29" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2236,6 +2751,30 @@
       <c r="O30" s="5" t="n">
         <v>0.8911</v>
       </c>
+      <c r="P30" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U30" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V30" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W30" s="6" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2297,6 +2836,30 @@
       <c r="O31" s="5" t="n">
         <v>0.8911</v>
       </c>
+      <c r="P31" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2358,6 +2921,30 @@
       <c r="O32" s="5" t="n">
         <v>0.9699</v>
       </c>
+      <c r="P32" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W32" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2419,6 +3006,14 @@
       <c r="O33" s="5" t="n">
         <v>0.8918</v>
       </c>
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr"/>
+      <c r="W33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2466,6 +3061,14 @@
       <c r="O34" s="5" t="n">
         <v>0.9032</v>
       </c>
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr"/>
+      <c r="V34" s="6" t="inlineStr"/>
+      <c r="W34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2513,6 +3116,14 @@
       <c r="O35" s="5" t="n">
         <v>0.9695</v>
       </c>
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr"/>
+      <c r="W35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2574,6 +3185,30 @@
       <c r="O36" s="5" t="n">
         <v>0.8218</v>
       </c>
+      <c r="P36" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2634,6 +3269,30 @@
       </c>
       <c r="O37" s="5" t="n">
         <v>0.8865</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V37" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W37" s="6" t="n">
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -2692,6 +3351,14 @@
       <c r="O38" s="5" t="n">
         <v>0.9273</v>
       </c>
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr"/>
+      <c r="W38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2749,6 +3416,30 @@
       <c r="O39" s="5" t="n">
         <v>0.9427</v>
       </c>
+      <c r="P39" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2806,6 +3497,30 @@
       <c r="O40" s="5" t="n">
         <v>0.9427</v>
       </c>
+      <c r="P40" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2867,6 +3582,30 @@
       <c r="O41" s="5" t="n">
         <v>0.9091</v>
       </c>
+      <c r="P41" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2927,6 +3666,30 @@
       </c>
       <c r="O42" s="5" t="n">
         <v>0.8824</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U42" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V42" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W42" s="6" t="n">
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -2985,6 +3748,14 @@
       <c r="O43" s="5" t="n">
         <v>0.8908</v>
       </c>
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3042,6 +3813,14 @@
       <c r="O44" s="5" t="n">
         <v>0.8894</v>
       </c>
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr"/>
+      <c r="V44" s="6" t="inlineStr"/>
+      <c r="W44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3101,6 +3880,30 @@
       <c r="O45" s="5" t="n">
         <v>0.9376</v>
       </c>
+      <c r="P45" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S45" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T45" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U45" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V45" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W45" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3162,6 +3965,30 @@
       <c r="O46" s="5" t="n">
         <v>0.9273</v>
       </c>
+      <c r="P46" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="T46" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="U46" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V46" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W46" s="6" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3223,6 +4050,14 @@
       <c r="O47" s="5" t="n">
         <v>0.8865</v>
       </c>
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr"/>
+      <c r="W47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3283,6 +4118,30 @@
       </c>
       <c r="O48" s="5" t="n">
         <v>0.8265</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S48" s="6" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="T48" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="U48" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="V48" s="6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W48" s="6" t="n">
+        <v>0.2533333333333334</v>
       </c>
     </row>
     <row r="49">
@@ -3341,6 +4200,14 @@
       <c r="O49" s="5" t="n">
         <v>0.955</v>
       </c>
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr"/>
+      <c r="W49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3402,6 +4269,14 @@
       <c r="O50" s="5" t="n">
         <v>0.8865</v>
       </c>
+      <c r="P50" s="6" t="inlineStr"/>
+      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr"/>
+      <c r="W50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3453,6 +4328,14 @@
       <c r="O51" s="5" t="n">
         <v>0.9254</v>
       </c>
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr"/>
+      <c r="W51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3504,6 +4387,14 @@
       <c r="O52" s="5" t="n">
         <v>0.9391</v>
       </c>
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr"/>
+      <c r="W52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3555,6 +4446,14 @@
       <c r="O53" s="5" t="n">
         <v>0.9638</v>
       </c>
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr"/>
+      <c r="W53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3606,6 +4505,14 @@
       <c r="O54" s="5" t="n">
         <v>0.9545</v>
       </c>
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr"/>
+      <c r="W54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3653,6 +4560,14 @@
       <c r="O55" s="5" t="n">
         <v>0.9694</v>
       </c>
+      <c r="P55" s="6" t="inlineStr"/>
+      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr"/>
+      <c r="W55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3704,6 +4619,14 @@
       <c r="O56" s="5" t="n">
         <v>0.9643</v>
       </c>
+      <c r="P56" s="6" t="inlineStr"/>
+      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr"/>
+      <c r="V56" s="6" t="inlineStr"/>
+      <c r="W56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3751,6 +4674,14 @@
       <c r="O57" s="5" t="n">
         <v>0.9644</v>
       </c>
+      <c r="P57" s="6" t="inlineStr"/>
+      <c r="Q57" s="6" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr"/>
+      <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3798,6 +4729,14 @@
       <c r="O58" s="5" t="n">
         <v>0.9641999999999999</v>
       </c>
+      <c r="P58" s="6" t="inlineStr"/>
+      <c r="Q58" s="6" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr"/>
+      <c r="T58" s="6" t="inlineStr"/>
+      <c r="U58" s="6" t="inlineStr"/>
+      <c r="V58" s="6" t="inlineStr"/>
+      <c r="W58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3849,6 +4788,14 @@
       <c r="O59" s="5" t="n">
         <v>0.9276</v>
       </c>
+      <c r="P59" s="6" t="inlineStr"/>
+      <c r="Q59" s="6" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr"/>
+      <c r="T59" s="6" t="inlineStr"/>
+      <c r="U59" s="6" t="inlineStr"/>
+      <c r="V59" s="6" t="inlineStr"/>
+      <c r="W59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3896,6 +4843,14 @@
       <c r="O60" s="5" t="n">
         <v>0.9528</v>
       </c>
+      <c r="P60" s="6" t="inlineStr"/>
+      <c r="Q60" s="6" t="inlineStr"/>
+      <c r="R60" s="6" t="inlineStr"/>
+      <c r="S60" s="6" t="inlineStr"/>
+      <c r="T60" s="6" t="inlineStr"/>
+      <c r="U60" s="6" t="inlineStr"/>
+      <c r="V60" s="6" t="inlineStr"/>
+      <c r="W60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3945,6 +4900,14 @@
       <c r="O61" s="5" t="n">
         <v>1.0047</v>
       </c>
+      <c r="P61" s="6" t="inlineStr"/>
+      <c r="Q61" s="6" t="inlineStr"/>
+      <c r="R61" s="6" t="inlineStr"/>
+      <c r="S61" s="6" t="inlineStr"/>
+      <c r="T61" s="6" t="inlineStr"/>
+      <c r="U61" s="6" t="inlineStr"/>
+      <c r="V61" s="6" t="inlineStr"/>
+      <c r="W61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3996,6 +4959,14 @@
       <c r="O62" s="5" t="n">
         <v>0.9635</v>
       </c>
+      <c r="P62" s="6" t="inlineStr"/>
+      <c r="Q62" s="6" t="inlineStr"/>
+      <c r="R62" s="6" t="inlineStr"/>
+      <c r="S62" s="6" t="inlineStr"/>
+      <c r="T62" s="6" t="inlineStr"/>
+      <c r="U62" s="6" t="inlineStr"/>
+      <c r="V62" s="6" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4047,6 +5018,14 @@
       <c r="O63" s="5" t="n">
         <v>0.9635</v>
       </c>
+      <c r="P63" s="6" t="inlineStr"/>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr"/>
+      <c r="S63" s="6" t="inlineStr"/>
+      <c r="T63" s="6" t="inlineStr"/>
+      <c r="U63" s="6" t="inlineStr"/>
+      <c r="V63" s="6" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4098,6 +5077,14 @@
       <c r="O64" s="5" t="n">
         <v>0.9528</v>
       </c>
+      <c r="P64" s="6" t="inlineStr"/>
+      <c r="Q64" s="6" t="inlineStr"/>
+      <c r="R64" s="6" t="inlineStr"/>
+      <c r="S64" s="6" t="inlineStr"/>
+      <c r="T64" s="6" t="inlineStr"/>
+      <c r="U64" s="6" t="inlineStr"/>
+      <c r="V64" s="6" t="inlineStr"/>
+      <c r="W64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4147,6 +5134,14 @@
       <c r="O65" s="5" t="n">
         <v>0.9618</v>
       </c>
+      <c r="P65" s="6" t="inlineStr"/>
+      <c r="Q65" s="6" t="inlineStr"/>
+      <c r="R65" s="6" t="inlineStr"/>
+      <c r="S65" s="6" t="inlineStr"/>
+      <c r="T65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr"/>
+      <c r="V65" s="6" t="inlineStr"/>
+      <c r="W65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4198,6 +5193,14 @@
       <c r="O66" s="5" t="n">
         <v>0.8661</v>
       </c>
+      <c r="P66" s="6" t="inlineStr"/>
+      <c r="Q66" s="6" t="inlineStr"/>
+      <c r="R66" s="6" t="inlineStr"/>
+      <c r="S66" s="6" t="inlineStr"/>
+      <c r="T66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr"/>
+      <c r="V66" s="6" t="inlineStr"/>
+      <c r="W66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4249,6 +5252,14 @@
       <c r="O67" s="5" t="n">
         <v>0.896</v>
       </c>
+      <c r="P67" s="6" t="inlineStr"/>
+      <c r="Q67" s="6" t="inlineStr"/>
+      <c r="R67" s="6" t="inlineStr"/>
+      <c r="S67" s="6" t="inlineStr"/>
+      <c r="T67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr"/>
+      <c r="V67" s="6" t="inlineStr"/>
+      <c r="W67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4300,6 +5311,14 @@
       <c r="O68" s="5" t="n">
         <v>1.0029</v>
       </c>
+      <c r="P68" s="6" t="inlineStr"/>
+      <c r="Q68" s="6" t="inlineStr"/>
+      <c r="R68" s="6" t="inlineStr"/>
+      <c r="S68" s="6" t="inlineStr"/>
+      <c r="T68" s="6" t="inlineStr"/>
+      <c r="U68" s="6" t="inlineStr"/>
+      <c r="V68" s="6" t="inlineStr"/>
+      <c r="W68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4351,6 +5370,14 @@
       <c r="O69" s="5" t="n">
         <v>0.8265</v>
       </c>
+      <c r="P69" s="6" t="inlineStr"/>
+      <c r="Q69" s="6" t="inlineStr"/>
+      <c r="R69" s="6" t="inlineStr"/>
+      <c r="S69" s="6" t="inlineStr"/>
+      <c r="T69" s="6" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr"/>
+      <c r="V69" s="6" t="inlineStr"/>
+      <c r="W69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4402,6 +5429,14 @@
       <c r="O70" s="5" t="n">
         <v>0.9694</v>
       </c>
+      <c r="P70" s="6" t="inlineStr"/>
+      <c r="Q70" s="6" t="inlineStr"/>
+      <c r="R70" s="6" t="inlineStr"/>
+      <c r="S70" s="6" t="inlineStr"/>
+      <c r="T70" s="6" t="inlineStr"/>
+      <c r="U70" s="6" t="inlineStr"/>
+      <c r="V70" s="6" t="inlineStr"/>
+      <c r="W70" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4414,7 +5449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4425,57 +5460,141 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>DUID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Fuel</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY25-26</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>MLF_FY26-27</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY23-24</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_NEAR</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>ELI_CURTAILMENT_MED</t>
         </is>
       </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_CURTAILMENT_AVG</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY1_LABEL</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY2_LABEL</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3</t>
+        </is>
+      </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_FY3_LABEL</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>AVLSF1</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4498,14 +5617,68 @@
       <c r="H2" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>BERYLSF1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4528,14 +5701,68 @@
       <c r="H3" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
+      <c r="I3" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>BOMENSF1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4558,14 +5785,68 @@
       <c r="H4" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>BROKENH1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4588,14 +5869,68 @@
       <c r="H5" s="5" t="n">
         <v>0.017550018083952</v>
       </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.06999999999999999</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>CESF1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4610,14 +5945,52 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>COLEASF1</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4640,14 +6013,52 @@
       <c r="H7" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>CRWASF1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4670,14 +6081,68 @@
       <c r="H8" s="5" t="n">
         <v>7.253613938629221e-05</v>
       </c>
+      <c r="I8" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>CUSF1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4692,14 +6157,52 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>DARLSF1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4722,14 +6225,52 @@
       <c r="H10" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>FINLYSF1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4752,14 +6293,52 @@
       <c r="H11" s="5" t="n">
         <v>0.264676213474225</v>
       </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>GESF1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4774,14 +6353,52 @@
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>GOONSF1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4804,14 +6421,68 @@
       <c r="H13" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
+      <c r="I13" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>GRIFSF1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4830,14 +6501,52 @@
       <c r="H14" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>GULLRSF1</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4860,14 +6569,52 @@
       <c r="H15" s="5" t="n">
         <v>0.000681438300925263</v>
       </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>GNNDHSF1</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4890,14 +6637,68 @@
       <c r="H16" s="5" t="n">
         <v>0.900375357730696</v>
       </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0.07666666666666667</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>HILLSTN1</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4920,14 +6721,52 @@
       <c r="H17" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>JEMALNG1</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4950,14 +6789,52 @@
       <c r="H18" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>JUNEESF1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -4980,14 +6857,68 @@
       <c r="H19" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>LIMOSF11</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5010,14 +6941,68 @@
       <c r="H20" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
+      <c r="I20" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>LIMOSF21</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5040,14 +7025,68 @@
       <c r="H21" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
+      <c r="I21" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>MANSLR1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5070,14 +7109,68 @@
       <c r="H22" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
+      <c r="I22" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>METZSF1</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5100,14 +7193,68 @@
       <c r="H23" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="I23" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>MOLNGSF1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5130,14 +7277,68 @@
       <c r="H24" s="5" t="n">
         <v>0.928940919385981</v>
       </c>
+      <c r="I24" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>MOREESF1</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5160,14 +7361,68 @@
       <c r="H25" s="5" t="n">
         <v>0.0686562187806459</v>
       </c>
+      <c r="I25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>0.07666666666666667</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>MLSP1</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5182,14 +7437,52 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="5" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>MULWASF1</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5200,14 +7493,52 @@
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>NASF1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5226,14 +7557,52 @@
       <c r="H28" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>NEVERSF1</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5256,14 +7625,68 @@
       <c r="H29" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="I29" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>NEWENSF1</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5286,14 +7709,68 @@
       <c r="H30" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="I30" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>NEWENSF2</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5316,14 +7793,68 @@
       <c r="H31" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="I31" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>NYNGAN1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5346,14 +7877,68 @@
       <c r="H32" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="I32" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>PARSF1</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5376,14 +7961,52 @@
       <c r="H33" s="5" t="n">
         <v>0.886109380719023</v>
       </c>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>QPSFB1</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5398,14 +8021,52 @@
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="5" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>ROYALLA1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5420,14 +8081,52 @@
       <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>SUNRSF1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5450,14 +8149,68 @@
       <c r="H36" s="5" t="n">
         <v>0.286268642359214</v>
       </c>
+      <c r="I36" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>SEBSF1</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5480,14 +8233,68 @@
       <c r="H37" s="5" t="n">
         <v>0.0362161714591237</v>
       </c>
+      <c r="I37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>SKSF1</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5506,14 +8313,52 @@
       <c r="H38" s="5" t="n">
         <v>0.000643212863569608</v>
       </c>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="5" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>STUBSF1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5532,14 +8377,68 @@
       <c r="H39" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
+      <c r="I39" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>STUBSF2</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5558,14 +8457,68 @@
       <c r="H40" s="5" t="n">
         <v>0.6001917294906</v>
       </c>
+      <c r="I40" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>SUNTPSF1</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5588,14 +8541,68 @@
       <c r="H41" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="I41" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>WAGGNSF1</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5618,14 +8625,68 @@
       <c r="H42" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>WLWLSF1</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5644,14 +8705,52 @@
       <c r="H43" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>WLWLSF2</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5670,14 +8769,52 @@
       <c r="H44" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>WELNSF1</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5698,14 +8835,68 @@
       <c r="H45" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="I45" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>WELLSF1</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5728,14 +8919,68 @@
       <c r="H46" s="5" t="n">
         <v>0.0670248501388058</v>
       </c>
+      <c r="I46" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>WSTWYSF1</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5758,14 +9003,52 @@
       <c r="H47" s="5" t="n">
         <v>0.0107432723897736</v>
       </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>WRSF1</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5788,14 +9071,68 @@
       <c r="H48" s="5" t="n">
         <v>0.0508351004251619</v>
       </c>
+      <c r="I48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0.1633333333333333</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0.2533333333333334</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>WOLARSF1</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5814,14 +9151,52 @@
       <c r="H49" s="5" t="n">
         <v>0.000581408571101005</v>
       </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr"/>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>WYASF1</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
@@ -5844,14 +9219,52 @@
       <c r="H50" s="5" t="n">
         <v>0.00631707880200049</v>
       </c>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr"/>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="inlineStr"/>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>BANGOWF1</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5870,14 +9283,52 @@
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr"/>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>BANGOWF2</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5896,14 +9347,52 @@
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr"/>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr"/>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>BOCORWF1</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5922,14 +9411,52 @@
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="inlineStr"/>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>BODWF1</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5948,14 +9475,52 @@
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr"/>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr"/>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr"/>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>CAPTL_WF</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5970,14 +9535,52 @@
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="inlineStr"/>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>COLWF01</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -5996,14 +9599,52 @@
       </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="inlineStr"/>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T56" s="5" t="inlineStr"/>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>CROOKWF2</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6018,14 +9659,52 @@
       <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T57" s="5" t="inlineStr"/>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>CROOKWF3</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6040,14 +9719,52 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr"/>
+      <c r="P58" s="5" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="inlineStr"/>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr"/>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>CRURWF1</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6066,14 +9783,52 @@
       </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr"/>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="inlineStr"/>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr"/>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>CULLRGWF</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6088,14 +9843,52 @@
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr"/>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R60" s="5" t="inlineStr"/>
+      <c r="S60" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T60" s="5" t="inlineStr"/>
+      <c r="U60" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>FLYCRKWF</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6112,14 +9905,52 @@
       </c>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr"/>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R61" s="5" t="inlineStr"/>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T61" s="5" t="inlineStr"/>
+      <c r="U61" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>GULLRWF1</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6138,14 +9969,52 @@
       </c>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr"/>
+      <c r="P62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R62" s="5" t="inlineStr"/>
+      <c r="S62" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T62" s="5" t="inlineStr"/>
+      <c r="U62" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>GULLRWF2</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6164,14 +10033,52 @@
       </c>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr"/>
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr"/>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T63" s="5" t="inlineStr"/>
+      <c r="U63" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>GUNNING1</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6190,14 +10097,52 @@
       </c>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr"/>
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="inlineStr"/>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T64" s="5" t="inlineStr"/>
+      <c r="U64" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>RYEPARK1</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6214,14 +10159,52 @@
       </c>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr"/>
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T65" s="5" t="inlineStr"/>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>SAPHWF1</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6240,14 +10223,52 @@
       </c>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr"/>
+      <c r="P66" s="5" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="inlineStr"/>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T66" s="5" t="inlineStr"/>
+      <c r="U66" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>STWF1</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6266,14 +10287,52 @@
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr"/>
+      <c r="P67" s="5" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>TARALGA1</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6292,14 +10351,52 @@
       </c>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr"/>
+      <c r="P68" s="5" t="inlineStr"/>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R68" s="5" t="inlineStr"/>
+      <c r="S68" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T68" s="5" t="inlineStr"/>
+      <c r="U68" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>WRWF1</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6318,14 +10415,52 @@
       </c>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr"/>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr"/>
+      <c r="P69" s="5" t="inlineStr"/>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R69" s="5" t="inlineStr"/>
+      <c r="S69" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T69" s="5" t="inlineStr"/>
+      <c r="U69" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>WOODLWN1</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Wind</t>
         </is>
@@ -6344,6 +10479,44 @@
       </c>
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr"/>
+      <c r="P70" s="5" t="inlineStr"/>
+      <c r="Q70" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R70" s="5" t="inlineStr"/>
+      <c r="S70" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T70" s="5" t="inlineStr"/>
+      <c r="U70" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V70" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C70">
@@ -6418,6 +10591,174 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I70">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J70">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K70">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L70">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M70">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N70">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O70">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P70">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q70">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R70">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S70">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T70">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U70">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V70">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -532,12 +532,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY23-24</t>
+          <t>Actual FY24-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Actual FY24-25</t>
+          <t>Actual FY25-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -644,11 +644,9 @@
         <v>132</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="K2" s="5" t="n">
         <v>0.1441</v>
       </c>
+      <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -729,11 +727,9 @@
         <v>66</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="K3" s="5" t="n">
         <v>0.128</v>
       </c>
+      <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -814,11 +810,9 @@
         <v>132</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="K4" s="5" t="n">
         <v>0.123</v>
       </c>
+      <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -899,11 +893,9 @@
         <v>22</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="K5" s="5" t="n">
         <v>0.1492</v>
       </c>
+      <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="n">
         <v>0.399270575823056</v>
       </c>
@@ -1039,11 +1031,9 @@
         <v>132</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.0327</v>
-      </c>
-      <c r="K7" s="5" t="n">
         <v>0.0292</v>
       </c>
+      <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -1108,11 +1098,9 @@
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.0862</v>
-      </c>
-      <c r="K8" s="5" t="n">
         <v>0.0799</v>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="n">
         <v>0.529503172508041</v>
       </c>
@@ -1248,11 +1236,9 @@
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.0636</v>
-      </c>
-      <c r="K10" s="5" t="n">
         <v>0.0833</v>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -1317,11 +1303,9 @@
         <v>132</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.0643</v>
-      </c>
-      <c r="K11" s="5" t="n">
         <v>0.0762</v>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="n">
         <v>0.7032826997896851</v>
       </c>
@@ -1441,11 +1425,9 @@
         <v>66</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="K13" s="5" t="n">
         <v>0.3285</v>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -1591,11 +1573,9 @@
         <v>330</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="K15" s="5" t="n">
         <v>0.1353</v>
       </c>
+      <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="5" t="n">
         <v>0.165388664850326</v>
       </c>
@@ -1660,11 +1640,9 @@
         <v>132</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1268</v>
-      </c>
-      <c r="K16" s="5" t="n">
         <v>0.1778</v>
       </c>
+      <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="n">
         <v>0.903607825126104</v>
       </c>
@@ -1745,11 +1723,9 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1304</v>
-      </c>
-      <c r="K17" s="5" t="n">
         <v>0.2781</v>
       </c>
+      <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -1814,11 +1790,9 @@
         <v>66</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-      <c r="K18" s="5" t="n">
         <v>0.1147</v>
       </c>
+      <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -1883,11 +1857,9 @@
         <v>132</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.1534</v>
-      </c>
-      <c r="K19" s="5" t="n">
         <v>0.2801</v>
       </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -1968,11 +1940,9 @@
         <v>220</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.1138</v>
-      </c>
-      <c r="K20" s="5" t="n">
         <v>0.2431</v>
       </c>
+      <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -2053,11 +2023,9 @@
         <v>22</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1244</v>
-      </c>
-      <c r="K21" s="5" t="n">
         <v>0.2403</v>
       </c>
+      <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -2138,11 +2106,9 @@
         <v>132</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.4514</v>
-      </c>
-      <c r="K22" s="5" t="n">
         <v>0.5511</v>
       </c>
+      <c r="K22" s="5" t="inlineStr"/>
       <c r="L22" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -2223,11 +2189,9 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="K23" s="5" t="n">
         <v>0.0614</v>
       </c>
+      <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -2308,11 +2272,9 @@
         <v>66</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="K24" s="5" t="n">
         <v>0.5639</v>
       </c>
+      <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -2393,11 +2355,9 @@
         <v>66</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K25" s="5" t="n">
         <v>0.0089</v>
       </c>
+      <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="n">
         <v>0.188257195450457</v>
       </c>
@@ -2649,11 +2609,9 @@
         <v>132</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="K29" s="5" t="n">
         <v>0.078</v>
       </c>
+      <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -2734,11 +2692,9 @@
         <v>330</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="K30" s="5" t="n">
         <v>0.125</v>
       </c>
+      <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -2819,11 +2775,9 @@
         <v>330</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0.0885</v>
-      </c>
-      <c r="K31" s="5" t="n">
         <v>0.1153</v>
       </c>
+      <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -2904,11 +2858,9 @@
         <v>132</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="K32" s="5" t="n">
         <v>0.0388</v>
       </c>
+      <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -2989,11 +2941,9 @@
         <v>66</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="K33" s="5" t="n">
         <v>0.2694</v>
       </c>
+      <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -3168,11 +3118,9 @@
         <v>220</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.1059</v>
-      </c>
-      <c r="K36" s="5" t="n">
         <v>0.1146</v>
       </c>
+      <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -3253,11 +3201,9 @@
         <v>132</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.1766</v>
-      </c>
-      <c r="K37" s="5" t="n">
         <v>0.2365</v>
       </c>
+      <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="5" t="n">
         <v>0.1571570475144</v>
       </c>
@@ -3565,11 +3511,9 @@
         <v>132</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.1231</v>
-      </c>
-      <c r="K41" s="5" t="n">
         <v>0.1167</v>
       </c>
+      <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -3650,11 +3594,9 @@
         <v>66</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0.1585</v>
-      </c>
-      <c r="K42" s="5" t="n">
         <v>0.2501</v>
       </c>
+      <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -3864,10 +3806,10 @@
       <c r="I45" s="2" t="n">
         <v>330</v>
       </c>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="n">
+      <c r="J45" s="5" t="n">
         <v>0.0616</v>
       </c>
+      <c r="K45" s="5" t="inlineStr"/>
       <c r="L45" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -3948,11 +3890,9 @@
         <v>132</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="K46" s="5" t="n">
         <v>0.0306</v>
       </c>
+      <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -4033,11 +3973,9 @@
         <v>132</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>0.1433</v>
-      </c>
-      <c r="K47" s="5" t="n">
         <v>0.1883</v>
       </c>
+      <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -4102,11 +4040,9 @@
         <v>132</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0.06519999999999999</v>
-      </c>
-      <c r="K48" s="5" t="n">
         <v>0.06469999999999999</v>
       </c>
+      <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -4252,11 +4188,9 @@
         <v>132</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>0.2031</v>
-      </c>
-      <c r="K50" s="5" t="n">
         <v>0.1969</v>
       </c>
+      <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -4315,11 +4249,9 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="5" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="K51" s="5" t="n">
         <v>0.0528</v>
       </c>
+      <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="n">
@@ -4374,11 +4306,9 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="K52" s="5" t="n">
         <v>0.1308</v>
       </c>
+      <c r="K52" s="5" t="inlineStr"/>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
@@ -4433,11 +4363,9 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K53" s="5" t="n">
         <v>0.0143</v>
       </c>
+      <c r="K53" s="5" t="inlineStr"/>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
@@ -4492,11 +4420,9 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="n">
-        <v>0.0213</v>
-      </c>
-      <c r="K54" s="5" t="n">
         <v>0.0265</v>
       </c>
+      <c r="K54" s="5" t="inlineStr"/>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
@@ -4606,11 +4532,9 @@
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="5" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="K56" s="5" t="n">
         <v>0.0066</v>
       </c>
+      <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="n">
@@ -4775,11 +4699,9 @@
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="5" t="n">
-        <v>0.0109</v>
-      </c>
-      <c r="K59" s="5" t="n">
         <v>0.0298</v>
       </c>
+      <c r="K59" s="5" t="inlineStr"/>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="n">
@@ -4888,10 +4810,10 @@
         <v>145</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="n">
+      <c r="J61" s="5" t="n">
         <v>0.0509</v>
       </c>
+      <c r="K61" s="5" t="inlineStr"/>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="n">
@@ -4946,11 +4868,9 @@
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="5" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="K62" s="5" t="n">
         <v>0.0168</v>
       </c>
+      <c r="K62" s="5" t="inlineStr"/>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="n">
@@ -5005,11 +4925,9 @@
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="5" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="K63" s="5" t="n">
         <v>0.055</v>
       </c>
+      <c r="K63" s="5" t="inlineStr"/>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
       <c r="N63" s="5" t="n">
@@ -5064,11 +4982,9 @@
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="5" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="K64" s="5" t="n">
         <v>0.0178</v>
       </c>
+      <c r="K64" s="5" t="inlineStr"/>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="n">
@@ -5122,10 +5038,10 @@
         <v>396</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="5" t="n">
+      <c r="J65" s="5" t="n">
         <v>0.0134</v>
       </c>
+      <c r="K65" s="5" t="inlineStr"/>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="n">
@@ -5180,11 +5096,9 @@
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="5" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="K66" s="5" t="n">
         <v>0.0056</v>
       </c>
+      <c r="K66" s="5" t="inlineStr"/>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
       <c r="N66" s="5" t="n">
@@ -5239,11 +5153,9 @@
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="5" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="K67" s="5" t="n">
         <v>0.064</v>
       </c>
+      <c r="K67" s="5" t="inlineStr"/>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="n">
@@ -5298,11 +5210,9 @@
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="5" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="K68" s="5" t="n">
         <v>0.0002</v>
       </c>
+      <c r="K68" s="5" t="inlineStr"/>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
       <c r="N68" s="5" t="n">
@@ -5357,11 +5267,9 @@
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="5" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="K69" s="5" t="n">
         <v>0.0573</v>
       </c>
+      <c r="K69" s="5" t="inlineStr"/>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
       <c r="N69" s="5" t="n">
@@ -5416,11 +5324,9 @@
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="5" t="n">
-        <v>0.0157</v>
-      </c>
-      <c r="K70" s="5" t="n">
         <v>0.0294</v>
       </c>
+      <c r="K70" s="5" t="inlineStr"/>
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr"/>
       <c r="N70" s="5" t="n">
@@ -5499,12 +5405,12 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY23-24</t>
+          <t>CURTAILMENT_ACTUAL_FY24-25</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>CURTAILMENT_ACTUAL_FY24-25</t>
+          <t>CURTAILMENT_ACTUAL_FY25-26</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
@@ -5606,11 +5512,9 @@
         <v>0.8395</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="F2" s="5" t="n">
         <v>0.1441</v>
       </c>
+      <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -5690,11 +5594,9 @@
         <v>0.9245</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="F3" s="5" t="n">
         <v>0.128</v>
       </c>
+      <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -5774,11 +5676,9 @@
         <v>0.8823</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="F4" s="5" t="n">
         <v>0.123</v>
       </c>
+      <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -5858,11 +5758,9 @@
         <v>0.8436</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="F5" s="5" t="n">
         <v>0.1492</v>
       </c>
+      <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="n">
         <v>0.399270575823056</v>
       </c>
@@ -6002,11 +5900,9 @@
         <v>0.8416</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.0327</v>
-      </c>
-      <c r="F7" s="5" t="n">
         <v>0.0292</v>
       </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -6070,11 +5966,9 @@
         <v>0.8899</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0862</v>
-      </c>
-      <c r="F8" s="5" t="n">
         <v>0.0799</v>
       </c>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="n">
         <v>0.529503172508041</v>
       </c>
@@ -6214,11 +6108,9 @@
         <v>0.8554</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0636</v>
-      </c>
-      <c r="F10" s="5" t="n">
         <v>0.0833</v>
       </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -6282,11 +6174,9 @@
         <v>0.8521</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0643</v>
-      </c>
-      <c r="F11" s="5" t="n">
         <v>0.0762</v>
       </c>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="n">
         <v>0.7032826997896851</v>
       </c>
@@ -6410,11 +6300,9 @@
         <v>0.8918</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="F13" s="5" t="n">
         <v>0.3285</v>
       </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -6558,11 +6446,9 @@
         <v>0.9635</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.0328</v>
-      </c>
-      <c r="F15" s="5" t="n">
         <v>0.1353</v>
       </c>
+      <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="n">
         <v>0.165388664850326</v>
       </c>
@@ -6626,11 +6512,9 @@
         <v>0.8463000000000001</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.1268</v>
-      </c>
-      <c r="F16" s="5" t="n">
         <v>0.1778</v>
       </c>
+      <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="n">
         <v>0.903607825126104</v>
       </c>
@@ -6710,11 +6594,9 @@
         <v>0.8652</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1304</v>
-      </c>
-      <c r="F17" s="5" t="n">
         <v>0.2781</v>
       </c>
+      <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -6778,11 +6660,9 @@
         <v>0.8962</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-      <c r="F18" s="5" t="n">
         <v>0.1147</v>
       </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -6846,11 +6726,9 @@
         <v>0.8865</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.1534</v>
-      </c>
-      <c r="F19" s="5" t="n">
         <v>0.2801</v>
       </c>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -6930,11 +6808,9 @@
         <v>0.8206</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.1138</v>
-      </c>
-      <c r="F20" s="5" t="n">
         <v>0.2431</v>
       </c>
+      <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -7014,11 +6890,9 @@
         <v>0.8268</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.1244</v>
-      </c>
-      <c r="F21" s="5" t="n">
         <v>0.2403</v>
       </c>
+      <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -7098,11 +6972,9 @@
         <v>0.9482</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.4514</v>
-      </c>
-      <c r="F22" s="5" t="n">
         <v>0.5511</v>
       </c>
+      <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -7182,11 +7054,9 @@
         <v>0.8657</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="F23" s="5" t="n">
         <v>0.0614</v>
       </c>
+      <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -7266,11 +7136,9 @@
         <v>0.9583</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="F24" s="5" t="n">
         <v>0.5639</v>
       </c>
+      <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -7350,11 +7218,9 @@
         <v>0.8509</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="F25" s="5" t="n">
         <v>0.0089</v>
       </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="n">
         <v>0.188257195450457</v>
       </c>
@@ -7614,11 +7480,9 @@
         <v>0.9273</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="F29" s="5" t="n">
         <v>0.078</v>
       </c>
+      <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -7698,11 +7562,9 @@
         <v>0.8911</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="F30" s="5" t="n">
         <v>0.125</v>
       </c>
+      <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -7782,11 +7644,9 @@
         <v>0.8911</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.0885</v>
-      </c>
-      <c r="F31" s="5" t="n">
         <v>0.1153</v>
       </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -7866,11 +7726,9 @@
         <v>0.9699</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="F32" s="5" t="n">
         <v>0.0388</v>
       </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -7950,11 +7808,9 @@
         <v>0.8918</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="F33" s="5" t="n">
         <v>0.2694</v>
       </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -8138,11 +7994,9 @@
         <v>0.8218</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.1059</v>
-      </c>
-      <c r="F36" s="5" t="n">
         <v>0.1146</v>
       </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -8222,11 +8076,9 @@
         <v>0.8865</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.1766</v>
-      </c>
-      <c r="F37" s="5" t="n">
         <v>0.2365</v>
       </c>
+      <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="n">
         <v>0.1571570475144</v>
       </c>
@@ -8530,11 +8382,9 @@
         <v>0.9091</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.1231</v>
-      </c>
-      <c r="F41" s="5" t="n">
         <v>0.1167</v>
       </c>
+      <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -8614,11 +8464,9 @@
         <v>0.8824</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1585</v>
-      </c>
-      <c r="F42" s="5" t="n">
         <v>0.2501</v>
       </c>
+      <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -8825,10 +8673,10 @@
       <c r="D45" s="5" t="n">
         <v>0.9376</v>
       </c>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="n">
+      <c r="E45" s="5" t="n">
         <v>0.0616</v>
       </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -8908,11 +8756,9 @@
         <v>0.9273</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="F46" s="5" t="n">
         <v>0.0306</v>
       </c>
+      <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -8992,11 +8838,9 @@
         <v>0.8865</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.1433</v>
-      </c>
-      <c r="F47" s="5" t="n">
         <v>0.1883</v>
       </c>
+      <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -9060,11 +8904,9 @@
         <v>0.8265</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.06519999999999999</v>
-      </c>
-      <c r="F48" s="5" t="n">
         <v>0.06469999999999999</v>
       </c>
+      <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -9208,11 +9050,9 @@
         <v>0.8865</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.2031</v>
-      </c>
-      <c r="F50" s="5" t="n">
         <v>0.1969</v>
       </c>
+      <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -9276,11 +9116,9 @@
         <v>0.9254</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="F51" s="5" t="n">
         <v>0.0528</v>
       </c>
+      <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
@@ -9340,11 +9178,9 @@
         <v>0.9391</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0983</v>
-      </c>
-      <c r="F52" s="5" t="n">
         <v>0.1308</v>
       </c>
+      <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
@@ -9404,11 +9240,9 @@
         <v>0.9638</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="F53" s="5" t="n">
         <v>0.0143</v>
       </c>
+      <c r="F53" s="5" t="inlineStr"/>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
@@ -9468,11 +9302,9 @@
         <v>0.9545</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.0213</v>
-      </c>
-      <c r="F54" s="5" t="n">
         <v>0.0265</v>
       </c>
+      <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
@@ -9592,11 +9424,9 @@
         <v>0.9643</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="F56" s="5" t="n">
         <v>0.0066</v>
       </c>
+      <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
@@ -9776,11 +9606,9 @@
         <v>0.9276</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.0109</v>
-      </c>
-      <c r="F59" s="5" t="n">
         <v>0.0298</v>
       </c>
+      <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
@@ -9899,10 +9727,10 @@
       <c r="D61" s="5" t="n">
         <v>1.0047</v>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="5" t="n">
+      <c r="E61" s="5" t="n">
         <v>0.0509</v>
       </c>
+      <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
@@ -9962,11 +9790,9 @@
         <v>0.9635</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="F62" s="5" t="n">
         <v>0.0168</v>
       </c>
+      <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
@@ -10026,11 +9852,9 @@
         <v>0.9635</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="F63" s="5" t="n">
         <v>0.055</v>
       </c>
+      <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
@@ -10090,11 +9914,9 @@
         <v>0.9528</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.0239</v>
-      </c>
-      <c r="F64" s="5" t="n">
         <v>0.0178</v>
       </c>
+      <c r="F64" s="5" t="inlineStr"/>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
@@ -10153,10 +9975,10 @@
       <c r="D65" s="5" t="n">
         <v>0.9618</v>
       </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="5" t="n">
+      <c r="E65" s="5" t="n">
         <v>0.0134</v>
       </c>
+      <c r="F65" s="5" t="inlineStr"/>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
@@ -10216,11 +10038,9 @@
         <v>0.8661</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="F66" s="5" t="n">
         <v>0.0056</v>
       </c>
+      <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
@@ -10280,11 +10100,9 @@
         <v>0.896</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.0354</v>
-      </c>
-      <c r="F67" s="5" t="n">
         <v>0.064</v>
       </c>
+      <c r="F67" s="5" t="inlineStr"/>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
@@ -10344,11 +10162,9 @@
         <v>1.0029</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="F68" s="5" t="n">
         <v>0.0002</v>
       </c>
+      <c r="F68" s="5" t="inlineStr"/>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
@@ -10408,11 +10224,9 @@
         <v>0.8265</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="F69" s="5" t="n">
         <v>0.0573</v>
       </c>
+      <c r="F69" s="5" t="inlineStr"/>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
@@ -10472,11 +10286,9 @@
         <v>0.9694</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.0157</v>
-      </c>
-      <c r="F70" s="5" t="n">
         <v>0.0294</v>
       </c>
+      <c r="F70" s="5" t="inlineStr"/>
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>

--- a/outputs/NSW_curtailment.xlsx
+++ b/outputs/NSW_curtailment.xlsx
@@ -646,7 +646,9 @@
       <c r="J2" s="5" t="n">
         <v>0.1441</v>
       </c>
-      <c r="K2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="n">
+        <v>0.1695</v>
+      </c>
       <c r="L2" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -729,7 +731,9 @@
       <c r="J3" s="5" t="n">
         <v>0.128</v>
       </c>
-      <c r="K3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="n">
+        <v>0.078</v>
+      </c>
       <c r="L3" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -812,7 +816,9 @@
       <c r="J4" s="5" t="n">
         <v>0.123</v>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
+        <v>0.1001</v>
+      </c>
       <c r="L4" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -895,7 +901,9 @@
       <c r="J5" s="5" t="n">
         <v>0.1492</v>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>0.2117</v>
+      </c>
       <c r="L5" s="5" t="n">
         <v>0.399270575823056</v>
       </c>
@@ -1033,7 +1041,9 @@
       <c r="J7" s="5" t="n">
         <v>0.0292</v>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>0.0415</v>
+      </c>
       <c r="L7" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -1100,7 +1110,9 @@
       <c r="J8" s="5" t="n">
         <v>0.0799</v>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
+        <v>0.1689</v>
+      </c>
       <c r="L8" s="5" t="n">
         <v>0.529503172508041</v>
       </c>
@@ -1175,7 +1187,9 @@
       </c>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n">
+        <v>0.342</v>
+      </c>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
       <c r="N9" s="5" t="n">
@@ -1238,7 +1252,9 @@
       <c r="J10" s="5" t="n">
         <v>0.0833</v>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>0.1175</v>
+      </c>
       <c r="L10" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -1427,7 +1443,9 @@
       <c r="J13" s="5" t="n">
         <v>0.3285</v>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="n">
+        <v>0.3999</v>
+      </c>
       <c r="L13" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -1575,7 +1593,9 @@
       <c r="J15" s="5" t="n">
         <v>0.1353</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="n">
+        <v>0.2162</v>
+      </c>
       <c r="L15" s="5" t="n">
         <v>0.165388664850326</v>
       </c>
@@ -1642,7 +1662,9 @@
       <c r="J16" s="5" t="n">
         <v>0.1778</v>
       </c>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="n">
+        <v>0.2693</v>
+      </c>
       <c r="L16" s="5" t="n">
         <v>0.903607825126104</v>
       </c>
@@ -1725,7 +1747,9 @@
       <c r="J17" s="5" t="n">
         <v>0.2781</v>
       </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="n">
+        <v>0.1928</v>
+      </c>
       <c r="L17" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -1792,7 +1816,9 @@
       <c r="J18" s="5" t="n">
         <v>0.1147</v>
       </c>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="n">
+        <v>0.3103</v>
+      </c>
       <c r="L18" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -1859,7 +1885,9 @@
       <c r="J19" s="5" t="n">
         <v>0.2801</v>
       </c>
-      <c r="K19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="n">
+        <v>0.2607</v>
+      </c>
       <c r="L19" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -1942,7 +1970,9 @@
       <c r="J20" s="5" t="n">
         <v>0.2431</v>
       </c>
-      <c r="K20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="n">
+        <v>0.2125</v>
+      </c>
       <c r="L20" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -2025,7 +2055,9 @@
       <c r="J21" s="5" t="n">
         <v>0.2403</v>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="n">
+        <v>0.1922</v>
+      </c>
       <c r="L21" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -2108,7 +2140,9 @@
       <c r="J22" s="5" t="n">
         <v>0.5511</v>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
+        <v>0.5341</v>
+      </c>
       <c r="L22" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -2191,7 +2225,9 @@
       <c r="J23" s="5" t="n">
         <v>0.0614</v>
       </c>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
+        <v>0.1487</v>
+      </c>
       <c r="L23" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -2274,7 +2310,9 @@
       <c r="J24" s="5" t="n">
         <v>0.5639</v>
       </c>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
+        <v>0.3973</v>
+      </c>
       <c r="L24" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -2357,7 +2395,9 @@
       <c r="J25" s="5" t="n">
         <v>0.0089</v>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
+        <v>0.0169</v>
+      </c>
       <c r="L25" s="5" t="n">
         <v>0.188257195450457</v>
       </c>
@@ -2611,7 +2651,9 @@
       <c r="J29" s="5" t="n">
         <v>0.078</v>
       </c>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="n">
+        <v>0.2905</v>
+      </c>
       <c r="L29" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -2694,7 +2736,9 @@
       <c r="J30" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="n">
+        <v>0.0318</v>
+      </c>
       <c r="L30" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -2777,7 +2821,9 @@
       <c r="J31" s="5" t="n">
         <v>0.1153</v>
       </c>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="n">
+        <v>0.036</v>
+      </c>
       <c r="L31" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -2860,7 +2906,9 @@
       <c r="J32" s="5" t="n">
         <v>0.0388</v>
       </c>
-      <c r="K32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="n">
+        <v>0.2983</v>
+      </c>
       <c r="L32" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -2943,7 +2991,9 @@
       <c r="J33" s="5" t="n">
         <v>0.2694</v>
       </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
+        <v>0.2848</v>
+      </c>
       <c r="L33" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -3120,7 +3170,9 @@
       <c r="J36" s="5" t="n">
         <v>0.1146</v>
       </c>
-      <c r="K36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="n">
+        <v>0.0936</v>
+      </c>
       <c r="L36" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -3203,7 +3255,9 @@
       <c r="J37" s="5" t="n">
         <v>0.2365</v>
       </c>
-      <c r="K37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="n">
+        <v>0.2465</v>
+      </c>
       <c r="L37" s="5" t="n">
         <v>0.1571570475144</v>
       </c>
@@ -3349,7 +3403,9 @@
         <v>330</v>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="n">
+        <v>0.08939999999999999</v>
+      </c>
       <c r="L39" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -3430,7 +3486,9 @@
         <v>330</v>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="n">
+        <v>0.0813</v>
+      </c>
       <c r="L40" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -3513,7 +3571,9 @@
       <c r="J41" s="5" t="n">
         <v>0.1167</v>
       </c>
-      <c r="K41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="n">
+        <v>0.2803</v>
+      </c>
       <c r="L41" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -3596,7 +3656,9 @@
       <c r="J42" s="5" t="n">
         <v>0.2501</v>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="n">
+        <v>0.2261</v>
+      </c>
       <c r="L42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -3677,7 +3739,9 @@
         <v>330</v>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="n">
+        <v>0.2674</v>
+      </c>
       <c r="L43" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -3742,7 +3806,9 @@
         <v>330</v>
       </c>
       <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="n">
+        <v>0.2715</v>
+      </c>
       <c r="L44" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -3809,7 +3875,9 @@
       <c r="J45" s="5" t="n">
         <v>0.0616</v>
       </c>
-      <c r="K45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="n">
+        <v>0.0283</v>
+      </c>
       <c r="L45" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -3892,7 +3960,9 @@
       <c r="J46" s="5" t="n">
         <v>0.0306</v>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
+        <v>0.081</v>
+      </c>
       <c r="L46" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -3975,7 +4045,9 @@
       <c r="J47" s="5" t="n">
         <v>0.1883</v>
       </c>
-      <c r="K47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
+        <v>0.1353</v>
+      </c>
       <c r="L47" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -4042,7 +4114,9 @@
       <c r="J48" s="5" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="K48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="n">
+        <v>0.0301</v>
+      </c>
       <c r="L48" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -4123,7 +4197,9 @@
         <v>330</v>
       </c>
       <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="n">
+        <v>0.0216</v>
+      </c>
       <c r="L49" s="5" t="n">
         <v>0.158699742317549</v>
       </c>
@@ -4190,7 +4266,9 @@
       <c r="J50" s="5" t="n">
         <v>0.1969</v>
       </c>
-      <c r="K50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="n">
+        <v>0.1655</v>
+      </c>
       <c r="L50" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -4251,7 +4329,9 @@
       <c r="J51" s="5" t="n">
         <v>0.0528</v>
       </c>
-      <c r="K51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="n">
+        <v>0.0629</v>
+      </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="n">
@@ -4308,7 +4388,9 @@
       <c r="J52" s="5" t="n">
         <v>0.1308</v>
       </c>
-      <c r="K52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="n">
+        <v>0.1312</v>
+      </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="n">
@@ -4365,7 +4447,9 @@
       <c r="J53" s="5" t="n">
         <v>0.0143</v>
       </c>
-      <c r="K53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="n">
+        <v>0.0042</v>
+      </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="n">
@@ -4422,7 +4506,9 @@
       <c r="J54" s="5" t="n">
         <v>0.0265</v>
       </c>
-      <c r="K54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="n">
+        <v>0.0185</v>
+      </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="n">
@@ -4534,7 +4620,9 @@
       <c r="J56" s="5" t="n">
         <v>0.0066</v>
       </c>
-      <c r="K56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="n">
+        <v>0.0089</v>
+      </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="n">
@@ -4589,7 +4677,9 @@
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="n">
+        <v>0.0144</v>
+      </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="n">
@@ -4644,7 +4734,9 @@
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="n">
+        <v>0.0219</v>
+      </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="n">
@@ -4701,7 +4793,9 @@
       <c r="J59" s="5" t="n">
         <v>0.0298</v>
       </c>
-      <c r="K59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="n">
+        <v>0.0184</v>
+      </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="n">
@@ -4813,7 +4907,9 @@
       <c r="J61" s="5" t="n">
         <v>0.0509</v>
       </c>
-      <c r="K61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="n">
+        <v>0.019</v>
+      </c>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="n">
@@ -4870,7 +4966,9 @@
       <c r="J62" s="5" t="n">
         <v>0.0168</v>
       </c>
-      <c r="K62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="n">
+        <v>0.0077</v>
+      </c>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="n">
@@ -4927,7 +5025,9 @@
       <c r="J63" s="5" t="n">
         <v>0.055</v>
       </c>
-      <c r="K63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="n">
+        <v>0.009900000000000001</v>
+      </c>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
       <c r="N63" s="5" t="n">
@@ -4984,7 +5084,9 @@
       <c r="J64" s="5" t="n">
         <v>0.0178</v>
       </c>
-      <c r="K64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="n">
+        <v>0.0214</v>
+      </c>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="n">
@@ -5041,7 +5143,9 @@
       <c r="J65" s="5" t="n">
         <v>0.0134</v>
       </c>
-      <c r="K65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="n">
+        <v>0.0043</v>
+      </c>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
       <c r="N65" s="5" t="n">
@@ -5098,7 +5202,9 @@
       <c r="J66" s="5" t="n">
         <v>0.0056</v>
       </c>
-      <c r="K66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="n">
+        <v>0.0102</v>
+      </c>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
       <c r="N66" s="5" t="n">
@@ -5155,7 +5261,9 @@
       <c r="J67" s="5" t="n">
         <v>0.064</v>
       </c>
-      <c r="K67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="n">
+        <v>0.07679999999999999</v>
+      </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="n">
@@ -5212,7 +5320,9 @@
       <c r="J68" s="5" t="n">
         <v>0.0002</v>
       </c>
-      <c r="K68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="n">
+        <v>0.0035</v>
+      </c>
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
       <c r="N68" s="5" t="n">
@@ -5269,7 +5379,9 @@
       <c r="J69" s="5" t="n">
         <v>0.0573</v>
       </c>
-      <c r="K69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="n">
+        <v>0.0549</v>
+      </c>
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr"/>
       <c r="N69" s="5" t="n">
@@ -5326,7 +5438,9 @@
       <c r="J70" s="5" t="n">
         <v>0.0294</v>
       </c>
-      <c r="K70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="n">
+        <v>0.023</v>
+      </c>
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr"/>
       <c r="N70" s="5" t="n">
@@ -5514,7 +5628,9 @@
       <c r="E2" s="5" t="n">
         <v>0.1441</v>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>0.1695</v>
+      </c>
       <c r="G2" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -5596,7 +5712,9 @@
       <c r="E3" s="5" t="n">
         <v>0.128</v>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="n">
+        <v>0.078</v>
+      </c>
       <c r="G3" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -5678,7 +5796,9 @@
       <c r="E4" s="5" t="n">
         <v>0.123</v>
       </c>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>0.1001</v>
+      </c>
       <c r="G4" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -5760,7 +5880,9 @@
       <c r="E5" s="5" t="n">
         <v>0.1492</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0.2117</v>
+      </c>
       <c r="G5" s="5" t="n">
         <v>0.399270575823056</v>
       </c>
@@ -5902,7 +6024,9 @@
       <c r="E7" s="5" t="n">
         <v>0.0292</v>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>0.0415</v>
+      </c>
       <c r="G7" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -5968,7 +6092,9 @@
       <c r="E8" s="5" t="n">
         <v>0.0799</v>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>0.1689</v>
+      </c>
       <c r="G8" s="5" t="n">
         <v>0.529503172508041</v>
       </c>
@@ -6048,7 +6174,9 @@
         <v>0.8903</v>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>0.342</v>
+      </c>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
@@ -6110,7 +6238,9 @@
       <c r="E10" s="5" t="n">
         <v>0.0833</v>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>0.1175</v>
+      </c>
       <c r="G10" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -6302,7 +6432,9 @@
       <c r="E13" s="5" t="n">
         <v>0.3285</v>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="n">
+        <v>0.3999</v>
+      </c>
       <c r="G13" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -6448,7 +6580,9 @@
       <c r="E15" s="5" t="n">
         <v>0.1353</v>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>0.2162</v>
+      </c>
       <c r="G15" s="5" t="n">
         <v>0.165388664850326</v>
       </c>
@@ -6514,7 +6648,9 @@
       <c r="E16" s="5" t="n">
         <v>0.1778</v>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="n">
+        <v>0.2693</v>
+      </c>
       <c r="G16" s="5" t="n">
         <v>0.903607825126104</v>
       </c>
@@ -6596,7 +6732,9 @@
       <c r="E17" s="5" t="n">
         <v>0.2781</v>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>0.1928</v>
+      </c>
       <c r="G17" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -6662,7 +6800,9 @@
       <c r="E18" s="5" t="n">
         <v>0.1147</v>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="n">
+        <v>0.3103</v>
+      </c>
       <c r="G18" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -6728,7 +6868,9 @@
       <c r="E19" s="5" t="n">
         <v>0.2801</v>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>0.2607</v>
+      </c>
       <c r="G19" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -6810,7 +6952,9 @@
       <c r="E20" s="5" t="n">
         <v>0.2431</v>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>0.2125</v>
+      </c>
       <c r="G20" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -6892,7 +7036,9 @@
       <c r="E21" s="5" t="n">
         <v>0.2403</v>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>0.1922</v>
+      </c>
       <c r="G21" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -6974,7 +7120,9 @@
       <c r="E22" s="5" t="n">
         <v>0.5511</v>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>0.5341</v>
+      </c>
       <c r="G22" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -7056,7 +7204,9 @@
       <c r="E23" s="5" t="n">
         <v>0.0614</v>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>0.1487</v>
+      </c>
       <c r="G23" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -7138,7 +7288,9 @@
       <c r="E24" s="5" t="n">
         <v>0.5639</v>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="n">
+        <v>0.3973</v>
+      </c>
       <c r="G24" s="5" t="n">
         <v>0.919931770355409</v>
       </c>
@@ -7220,7 +7372,9 @@
       <c r="E25" s="5" t="n">
         <v>0.0089</v>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>0.0169</v>
+      </c>
       <c r="G25" s="5" t="n">
         <v>0.188257195450457</v>
       </c>
@@ -7482,7 +7636,9 @@
       <c r="E29" s="5" t="n">
         <v>0.078</v>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>0.2905</v>
+      </c>
       <c r="G29" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -7564,7 +7720,9 @@
       <c r="E30" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>0.0318</v>
+      </c>
       <c r="G30" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -7646,7 +7804,9 @@
       <c r="E31" s="5" t="n">
         <v>0.1153</v>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="n">
+        <v>0.036</v>
+      </c>
       <c r="G31" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -7728,7 +7888,9 @@
       <c r="E32" s="5" t="n">
         <v>0.0388</v>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>0.2983</v>
+      </c>
       <c r="G32" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -7810,7 +7972,9 @@
       <c r="E33" s="5" t="n">
         <v>0.2694</v>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>0.2848</v>
+      </c>
       <c r="G33" s="5" t="n">
         <v>0.87127903942823</v>
       </c>
@@ -7996,7 +8160,9 @@
       <c r="E36" s="5" t="n">
         <v>0.1146</v>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>0.0936</v>
+      </c>
       <c r="G36" s="5" t="n">
         <v>0.505349468159863</v>
       </c>
@@ -8078,7 +8244,9 @@
       <c r="E37" s="5" t="n">
         <v>0.2365</v>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>0.2465</v>
+      </c>
       <c r="G37" s="5" t="n">
         <v>0.1571570475144</v>
       </c>
@@ -8222,7 +8390,9 @@
         <v>0.9427</v>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>0.08939999999999999</v>
+      </c>
       <c r="G39" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -8302,7 +8472,9 @@
         <v>0.9427</v>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="n">
+        <v>0.0813</v>
+      </c>
       <c r="G40" s="5" t="n">
         <v>0.636442356808484</v>
       </c>
@@ -8384,7 +8556,9 @@
       <c r="E41" s="5" t="n">
         <v>0.1167</v>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="n">
+        <v>0.2803</v>
+      </c>
       <c r="G41" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -8466,7 +8640,9 @@
       <c r="E42" s="5" t="n">
         <v>0.2501</v>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>0.2261</v>
+      </c>
       <c r="G42" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -8546,7 +8722,9 @@
         <v>0.8908</v>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="n">
+        <v>0.2674</v>
+      </c>
       <c r="G43" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -8610,7 +8788,9 @@
         <v>0.8894</v>
       </c>
       <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="n">
+        <v>0.2715</v>
+      </c>
       <c r="G44" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -8676,7 +8856,9 @@
       <c r="E45" s="5" t="n">
         <v>0.0616</v>
       </c>
-      <c r="F45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>0.0283</v>
+      </c>
       <c r="G45" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -8758,7 +8940,9 @@
       <c r="E46" s="5" t="n">
         <v>0.0306</v>
       </c>
-      <c r="F46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>0.081</v>
+      </c>
       <c r="G46" s="5" t="n">
         <v>0.15663609258386</v>
       </c>
@@ -8840,7 +9024,9 @@
       <c r="E47" s="5" t="n">
         <v>0.1883</v>
       </c>
-      <c r="F47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>0.1353</v>
+      </c>
       <c r="G47" s="5" t="n">
         <v>0.64186785726147</v>
       </c>
@@ -8906,7 +9092,9 @@
       <c r="E48" s="5" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="F48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>0.0301</v>
+      </c>
       <c r="G48" s="5" t="n">
         <v>0.231026075027885</v>
       </c>
@@ -8986,7 +9174,9 @@
         <v>0.955</v>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>0.0216</v>
+      </c>
       <c r="G49" s="5" t="n">
         <v>0.158699742317549</v>
       </c>
@@ -9052,7 +9242,9 @@
       <c r="E50" s="5" t="n">
         <v>0.1969</v>
       </c>
-      <c r="F50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="n">
+        <v>0.1655</v>
+      </c>
       <c r="G50" s="5" t="n">
         <v>0.5859908275658871</v>
       </c>
@@ -9118,7 +9310,9 @@
       <c r="E51" s="5" t="n">
         <v>0.0528</v>
       </c>
-      <c r="F51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="n">
+        <v>0.0629</v>
+      </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
@@ -9180,7 +9374,9 @@
       <c r="E52" s="5" t="n">
         <v>0.1308</v>
       </c>
-      <c r="F52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="n">
+        <v>0.1312</v>
+      </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
@@ -9242,7 +9438,9 @@
       <c r="E53" s="5" t="n">
         <v>0.0143</v>
       </c>
-      <c r="F53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="n">
+        <v>0.0042</v>
+      </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
@@ -9304,7 +9502,9 @@
       <c r="E54" s="5" t="n">
         <v>0.0265</v>
       </c>
-      <c r="F54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="n">
+        <v>0.0185</v>
+      </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
@@ -9426,7 +9626,9 @@
       <c r="E56" s="5" t="n">
         <v>0.0066</v>
       </c>
-      <c r="F56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="n">
+        <v>0.0089</v>
+      </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
@@ -9486,7 +9688,9 @@
         <v>0.9644</v>
       </c>
       <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="n">
+        <v>0.0144</v>
+      </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
@@ -9546,7 +9750,9 @@
         <v>0.9641999999999999</v>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="n">
+        <v>0.0219</v>
+      </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
@@ -9608,7 +9814,9 @@
       <c r="E59" s="5" t="n">
         <v>0.0298</v>
       </c>
-      <c r="F59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="n">
+        <v>0.0184</v>
+      </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
@@ -9730,7 +9938,9 @@
       <c r="E61" s="5" t="n">
         <v>0.0509</v>
       </c>
-      <c r="F61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="n">
+        <v>0.019</v>
+      </c>
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
@@ -9792,7 +10002,9 @@
       <c r="E62" s="5" t="n">
         <v>0.0168</v>
       </c>
-      <c r="F62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="n">
+        <v>0.0077</v>
+      </c>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
@@ -9854,7 +10066,9 @@
       <c r="E63" s="5" t="n">
         <v>0.055</v>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="n">
+        <v>0.009900000000000001</v>
+      </c>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
@@ -9916,7 +10130,9 @@
       <c r="E64" s="5" t="n">
         <v>0.0178</v>
       </c>
-      <c r="F64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="n">
+        <v>0.0214</v>
+      </c>
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
@@ -9978,7 +10194,9 @@
       <c r="E65" s="5" t="n">
         <v>0.0134</v>
       </c>
-      <c r="F65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="n">
+        <v>0.0043</v>
+      </c>
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
@@ -10040,7 +10258,9 @@
       <c r="E66" s="5" t="n">
         <v>0.0056</v>
       </c>
-      <c r="F66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="n">
+        <v>0.0102</v>
+      </c>
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
@@ -10102,7 +10322,9 @@
       <c r="E67" s="5" t="n">
         <v>0.064</v>
       </c>
-      <c r="F67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="n">
+        <v>0.07679999999999999</v>
+      </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
@@ -10164,7 +10386,9 @@
       <c r="E68" s="5" t="n">
         <v>0.0002</v>
       </c>
-      <c r="F68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="n">
+        <v>0.0035</v>
+      </c>
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
@@ -10226,7 +10450,9 @@
       <c r="E69" s="5" t="n">
         <v>0.0573</v>
       </c>
-      <c r="F69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="n">
+        <v>0.0549</v>
+      </c>
       <c r="G69" s="5" t="inlineStr"/>
       <c r="H69" s="5" t="inlineStr"/>
       <c r="I69" s="5" t="inlineStr"/>
@@ -10288,7 +10514,9 @@
       <c r="E70" s="5" t="n">
         <v>0.0294</v>
       </c>
-      <c r="F70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="n">
+        <v>0.023</v>
+      </c>
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
